--- a/datos_reales.xlsx
+++ b/datos_reales.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acfestadistica\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F599F0A6-1545-40D1-BF2E-C07C97935A18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C10EAF30-40A1-4DD1-AC02-A260CBE5F87E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="891" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="999" uniqueCount="49">
   <si>
     <t>AÑO</t>
   </si>
@@ -5676,6 +5676,627 @@
         <v>6818</v>
       </c>
     </row>
+    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A223">
+        <v>2026</v>
+      </c>
+      <c r="B223" t="s">
+        <v>48</v>
+      </c>
+      <c r="C223">
+        <v>9</v>
+      </c>
+      <c r="D223" t="s">
+        <v>8</v>
+      </c>
+      <c r="E223" t="s">
+        <v>19</v>
+      </c>
+      <c r="F223" t="s">
+        <v>20</v>
+      </c>
+      <c r="G223">
+        <v>5885</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A224">
+        <v>2026</v>
+      </c>
+      <c r="B224" t="s">
+        <v>48</v>
+      </c>
+      <c r="C224">
+        <v>9</v>
+      </c>
+      <c r="D224" t="s">
+        <v>8</v>
+      </c>
+      <c r="E224" t="s">
+        <v>19</v>
+      </c>
+      <c r="F224" t="s">
+        <v>21</v>
+      </c>
+      <c r="G224">
+        <v>10627</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A225">
+        <v>2026</v>
+      </c>
+      <c r="B225" t="s">
+        <v>48</v>
+      </c>
+      <c r="C225">
+        <v>9</v>
+      </c>
+      <c r="D225" t="s">
+        <v>8</v>
+      </c>
+      <c r="E225" t="s">
+        <v>19</v>
+      </c>
+      <c r="F225" t="s">
+        <v>22</v>
+      </c>
+      <c r="G225">
+        <v>5960</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A226">
+        <v>2026</v>
+      </c>
+      <c r="B226" t="s">
+        <v>48</v>
+      </c>
+      <c r="C226">
+        <v>9</v>
+      </c>
+      <c r="D226" t="s">
+        <v>8</v>
+      </c>
+      <c r="E226" t="s">
+        <v>19</v>
+      </c>
+      <c r="F226" t="s">
+        <v>47</v>
+      </c>
+      <c r="G226">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A227">
+        <v>2026</v>
+      </c>
+      <c r="B227" t="s">
+        <v>48</v>
+      </c>
+      <c r="C227">
+        <v>9</v>
+      </c>
+      <c r="D227" t="s">
+        <v>9</v>
+      </c>
+      <c r="E227" t="s">
+        <v>19</v>
+      </c>
+      <c r="F227" t="s">
+        <v>23</v>
+      </c>
+      <c r="G227">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A228">
+        <v>2026</v>
+      </c>
+      <c r="B228" t="s">
+        <v>48</v>
+      </c>
+      <c r="C228">
+        <v>9</v>
+      </c>
+      <c r="D228" t="s">
+        <v>11</v>
+      </c>
+      <c r="E228" t="s">
+        <v>19</v>
+      </c>
+      <c r="F228" t="s">
+        <v>25</v>
+      </c>
+      <c r="G228">
+        <v>1326</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A229">
+        <v>2026</v>
+      </c>
+      <c r="B229" t="s">
+        <v>48</v>
+      </c>
+      <c r="C229">
+        <v>9</v>
+      </c>
+      <c r="D229" t="s">
+        <v>11</v>
+      </c>
+      <c r="E229" t="s">
+        <v>19</v>
+      </c>
+      <c r="F229" t="s">
+        <v>24</v>
+      </c>
+      <c r="G229">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A230">
+        <v>2026</v>
+      </c>
+      <c r="B230" t="s">
+        <v>48</v>
+      </c>
+      <c r="C230">
+        <v>9</v>
+      </c>
+      <c r="D230" t="s">
+        <v>12</v>
+      </c>
+      <c r="E230" t="s">
+        <v>19</v>
+      </c>
+      <c r="F230" t="s">
+        <v>26</v>
+      </c>
+      <c r="G230">
+        <v>14888</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A231">
+        <v>2026</v>
+      </c>
+      <c r="B231" t="s">
+        <v>48</v>
+      </c>
+      <c r="C231">
+        <v>9</v>
+      </c>
+      <c r="D231" t="s">
+        <v>12</v>
+      </c>
+      <c r="E231" t="s">
+        <v>19</v>
+      </c>
+      <c r="F231" t="s">
+        <v>27</v>
+      </c>
+      <c r="G231">
+        <v>4359</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A232">
+        <v>2026</v>
+      </c>
+      <c r="B232" t="s">
+        <v>48</v>
+      </c>
+      <c r="C232">
+        <v>9</v>
+      </c>
+      <c r="D232" t="s">
+        <v>12</v>
+      </c>
+      <c r="E232" t="s">
+        <v>19</v>
+      </c>
+      <c r="F232" t="s">
+        <v>28</v>
+      </c>
+      <c r="G232">
+        <v>8750</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A233">
+        <v>2026</v>
+      </c>
+      <c r="B233" t="s">
+        <v>48</v>
+      </c>
+      <c r="C233">
+        <v>9</v>
+      </c>
+      <c r="D233" t="s">
+        <v>12</v>
+      </c>
+      <c r="E233" t="s">
+        <v>19</v>
+      </c>
+      <c r="F233" t="s">
+        <v>29</v>
+      </c>
+      <c r="G233">
+        <v>6101</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A234">
+        <v>2026</v>
+      </c>
+      <c r="B234" t="s">
+        <v>48</v>
+      </c>
+      <c r="C234">
+        <v>9</v>
+      </c>
+      <c r="D234" t="s">
+        <v>13</v>
+      </c>
+      <c r="E234" t="s">
+        <v>19</v>
+      </c>
+      <c r="F234" t="s">
+        <v>30</v>
+      </c>
+      <c r="G234">
+        <v>1835</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A235">
+        <v>2026</v>
+      </c>
+      <c r="B235" t="s">
+        <v>48</v>
+      </c>
+      <c r="C235">
+        <v>9</v>
+      </c>
+      <c r="D235" t="s">
+        <v>14</v>
+      </c>
+      <c r="E235" t="s">
+        <v>19</v>
+      </c>
+      <c r="F235" t="s">
+        <v>31</v>
+      </c>
+      <c r="G235">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A236">
+        <v>2026</v>
+      </c>
+      <c r="B236" t="s">
+        <v>48</v>
+      </c>
+      <c r="C236">
+        <v>9</v>
+      </c>
+      <c r="D236" t="s">
+        <v>14</v>
+      </c>
+      <c r="E236" t="s">
+        <v>19</v>
+      </c>
+      <c r="F236" t="s">
+        <v>32</v>
+      </c>
+      <c r="G236">
+        <v>8101</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A237">
+        <v>2026</v>
+      </c>
+      <c r="B237" t="s">
+        <v>48</v>
+      </c>
+      <c r="C237">
+        <v>9</v>
+      </c>
+      <c r="D237" t="s">
+        <v>14</v>
+      </c>
+      <c r="E237" t="s">
+        <v>19</v>
+      </c>
+      <c r="F237" t="s">
+        <v>33</v>
+      </c>
+      <c r="G237">
+        <v>7230</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A238">
+        <v>2026</v>
+      </c>
+      <c r="B238" t="s">
+        <v>48</v>
+      </c>
+      <c r="C238">
+        <v>9</v>
+      </c>
+      <c r="D238" t="s">
+        <v>15</v>
+      </c>
+      <c r="E238" t="s">
+        <v>19</v>
+      </c>
+      <c r="F238" t="s">
+        <v>34</v>
+      </c>
+      <c r="G238">
+        <v>15390</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A239">
+        <v>2026</v>
+      </c>
+      <c r="B239" t="s">
+        <v>48</v>
+      </c>
+      <c r="C239">
+        <v>9</v>
+      </c>
+      <c r="D239" t="s">
+        <v>15</v>
+      </c>
+      <c r="E239" t="s">
+        <v>19</v>
+      </c>
+      <c r="F239" t="s">
+        <v>35</v>
+      </c>
+      <c r="G239">
+        <v>6383</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A240">
+        <v>2026</v>
+      </c>
+      <c r="B240" t="s">
+        <v>48</v>
+      </c>
+      <c r="C240">
+        <v>9</v>
+      </c>
+      <c r="D240" t="s">
+        <v>16</v>
+      </c>
+      <c r="E240" t="s">
+        <v>19</v>
+      </c>
+      <c r="F240" t="s">
+        <v>36</v>
+      </c>
+      <c r="G240">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A241">
+        <v>2026</v>
+      </c>
+      <c r="B241" t="s">
+        <v>48</v>
+      </c>
+      <c r="C241">
+        <v>9</v>
+      </c>
+      <c r="D241" t="s">
+        <v>16</v>
+      </c>
+      <c r="E241" t="s">
+        <v>19</v>
+      </c>
+      <c r="F241" t="s">
+        <v>37</v>
+      </c>
+      <c r="G241">
+        <v>1865</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A242">
+        <v>2026</v>
+      </c>
+      <c r="B242" t="s">
+        <v>48</v>
+      </c>
+      <c r="C242">
+        <v>9</v>
+      </c>
+      <c r="D242" t="s">
+        <v>16</v>
+      </c>
+      <c r="E242" t="s">
+        <v>19</v>
+      </c>
+      <c r="F242" t="s">
+        <v>38</v>
+      </c>
+      <c r="G242">
+        <v>1880</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A243">
+        <v>2026</v>
+      </c>
+      <c r="B243" t="s">
+        <v>48</v>
+      </c>
+      <c r="C243">
+        <v>9</v>
+      </c>
+      <c r="D243" t="s">
+        <v>16</v>
+      </c>
+      <c r="E243" t="s">
+        <v>19</v>
+      </c>
+      <c r="F243" t="s">
+        <v>39</v>
+      </c>
+      <c r="G243">
+        <v>16212</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A244">
+        <v>2026</v>
+      </c>
+      <c r="B244" t="s">
+        <v>48</v>
+      </c>
+      <c r="C244">
+        <v>9</v>
+      </c>
+      <c r="D244" t="s">
+        <v>17</v>
+      </c>
+      <c r="E244" t="s">
+        <v>17</v>
+      </c>
+      <c r="F244" t="s">
+        <v>40</v>
+      </c>
+      <c r="G244">
+        <v>74092</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A245">
+        <v>2026</v>
+      </c>
+      <c r="B245" t="s">
+        <v>48</v>
+      </c>
+      <c r="C245">
+        <v>9</v>
+      </c>
+      <c r="D245" t="s">
+        <v>18</v>
+      </c>
+      <c r="E245" t="s">
+        <v>19</v>
+      </c>
+      <c r="F245" t="s">
+        <v>41</v>
+      </c>
+      <c r="G245">
+        <v>3065</v>
+      </c>
+    </row>
+    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A246">
+        <v>2026</v>
+      </c>
+      <c r="B246" t="s">
+        <v>48</v>
+      </c>
+      <c r="C246">
+        <v>9</v>
+      </c>
+      <c r="D246" t="s">
+        <v>18</v>
+      </c>
+      <c r="E246" t="s">
+        <v>19</v>
+      </c>
+      <c r="F246" t="s">
+        <v>42</v>
+      </c>
+      <c r="G246">
+        <v>11869</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A247">
+        <v>2026</v>
+      </c>
+      <c r="B247" t="s">
+        <v>48</v>
+      </c>
+      <c r="C247">
+        <v>9</v>
+      </c>
+      <c r="D247" t="s">
+        <v>18</v>
+      </c>
+      <c r="E247" t="s">
+        <v>19</v>
+      </c>
+      <c r="F247" t="s">
+        <v>43</v>
+      </c>
+      <c r="G247">
+        <v>1482</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A248">
+        <v>2026</v>
+      </c>
+      <c r="B248" t="s">
+        <v>48</v>
+      </c>
+      <c r="C248">
+        <v>9</v>
+      </c>
+      <c r="D248" t="s">
+        <v>18</v>
+      </c>
+      <c r="E248" t="s">
+        <v>19</v>
+      </c>
+      <c r="F248" t="s">
+        <v>45</v>
+      </c>
+      <c r="G248">
+        <v>6481</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A249">
+        <v>2026</v>
+      </c>
+      <c r="B249" t="s">
+        <v>48</v>
+      </c>
+      <c r="C249">
+        <v>9</v>
+      </c>
+      <c r="D249" t="s">
+        <v>18</v>
+      </c>
+      <c r="E249" t="s">
+        <v>19</v>
+      </c>
+      <c r="F249" t="s">
+        <v>46</v>
+      </c>
+      <c r="G249">
+        <v>5668</v>
+      </c>
+    </row>
     <row r="771" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G771" s="2"/>
     </row>

--- a/datos_reales.xlsx
+++ b/datos_reales.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acfestadistica\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C10EAF30-40A1-4DD1-AC02-A260CBE5F87E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61ED7530-F906-4CBA-8270-CCFBED232F8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="999" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1107" uniqueCount="50">
   <si>
     <t>AÑO</t>
   </si>
@@ -183,6 +183,9 @@
   </si>
   <si>
     <t>FEBRERO</t>
+  </si>
+  <si>
+    <t>MARZO</t>
   </si>
 </sst>
 </file>
@@ -6297,6 +6300,627 @@
         <v>5668</v>
       </c>
     </row>
+    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A250">
+        <v>2026</v>
+      </c>
+      <c r="B250" t="s">
+        <v>49</v>
+      </c>
+      <c r="C250">
+        <v>10</v>
+      </c>
+      <c r="D250" t="s">
+        <v>8</v>
+      </c>
+      <c r="E250" t="s">
+        <v>19</v>
+      </c>
+      <c r="F250" t="s">
+        <v>20</v>
+      </c>
+      <c r="G250">
+        <v>7812</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A251">
+        <v>2026</v>
+      </c>
+      <c r="B251" t="s">
+        <v>49</v>
+      </c>
+      <c r="C251">
+        <v>10</v>
+      </c>
+      <c r="D251" t="s">
+        <v>8</v>
+      </c>
+      <c r="E251" t="s">
+        <v>19</v>
+      </c>
+      <c r="F251" t="s">
+        <v>21</v>
+      </c>
+      <c r="G251">
+        <v>10603</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A252">
+        <v>2026</v>
+      </c>
+      <c r="B252" t="s">
+        <v>49</v>
+      </c>
+      <c r="C252">
+        <v>10</v>
+      </c>
+      <c r="D252" t="s">
+        <v>8</v>
+      </c>
+      <c r="E252" t="s">
+        <v>19</v>
+      </c>
+      <c r="F252" t="s">
+        <v>22</v>
+      </c>
+      <c r="G252">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A253">
+        <v>2026</v>
+      </c>
+      <c r="B253" t="s">
+        <v>49</v>
+      </c>
+      <c r="C253">
+        <v>10</v>
+      </c>
+      <c r="D253" t="s">
+        <v>8</v>
+      </c>
+      <c r="E253" t="s">
+        <v>19</v>
+      </c>
+      <c r="F253" t="s">
+        <v>47</v>
+      </c>
+      <c r="G253">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A254">
+        <v>2026</v>
+      </c>
+      <c r="B254" t="s">
+        <v>49</v>
+      </c>
+      <c r="C254">
+        <v>10</v>
+      </c>
+      <c r="D254" t="s">
+        <v>9</v>
+      </c>
+      <c r="E254" t="s">
+        <v>19</v>
+      </c>
+      <c r="F254" t="s">
+        <v>23</v>
+      </c>
+      <c r="G254">
+        <v>2280</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A255">
+        <v>2026</v>
+      </c>
+      <c r="B255" t="s">
+        <v>49</v>
+      </c>
+      <c r="C255">
+        <v>10</v>
+      </c>
+      <c r="D255" t="s">
+        <v>11</v>
+      </c>
+      <c r="E255" t="s">
+        <v>19</v>
+      </c>
+      <c r="F255" t="s">
+        <v>25</v>
+      </c>
+      <c r="G255">
+        <v>2666</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A256">
+        <v>2026</v>
+      </c>
+      <c r="B256" t="s">
+        <v>49</v>
+      </c>
+      <c r="C256">
+        <v>10</v>
+      </c>
+      <c r="D256" t="s">
+        <v>11</v>
+      </c>
+      <c r="E256" t="s">
+        <v>19</v>
+      </c>
+      <c r="F256" t="s">
+        <v>24</v>
+      </c>
+      <c r="G256">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A257">
+        <v>2026</v>
+      </c>
+      <c r="B257" t="s">
+        <v>49</v>
+      </c>
+      <c r="C257">
+        <v>10</v>
+      </c>
+      <c r="D257" t="s">
+        <v>12</v>
+      </c>
+      <c r="E257" t="s">
+        <v>19</v>
+      </c>
+      <c r="F257" t="s">
+        <v>26</v>
+      </c>
+      <c r="G257">
+        <v>19960</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A258">
+        <v>2026</v>
+      </c>
+      <c r="B258" t="s">
+        <v>49</v>
+      </c>
+      <c r="C258">
+        <v>10</v>
+      </c>
+      <c r="D258" t="s">
+        <v>12</v>
+      </c>
+      <c r="E258" t="s">
+        <v>19</v>
+      </c>
+      <c r="F258" t="s">
+        <v>27</v>
+      </c>
+      <c r="G258">
+        <v>6412</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A259">
+        <v>2026</v>
+      </c>
+      <c r="B259" t="s">
+        <v>49</v>
+      </c>
+      <c r="C259">
+        <v>10</v>
+      </c>
+      <c r="D259" t="s">
+        <v>12</v>
+      </c>
+      <c r="E259" t="s">
+        <v>19</v>
+      </c>
+      <c r="F259" t="s">
+        <v>28</v>
+      </c>
+      <c r="G259">
+        <v>14410</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A260">
+        <v>2026</v>
+      </c>
+      <c r="B260" t="s">
+        <v>49</v>
+      </c>
+      <c r="C260">
+        <v>10</v>
+      </c>
+      <c r="D260" t="s">
+        <v>12</v>
+      </c>
+      <c r="E260" t="s">
+        <v>19</v>
+      </c>
+      <c r="F260" t="s">
+        <v>29</v>
+      </c>
+      <c r="G260">
+        <v>8070</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A261">
+        <v>2026</v>
+      </c>
+      <c r="B261" t="s">
+        <v>49</v>
+      </c>
+      <c r="C261">
+        <v>10</v>
+      </c>
+      <c r="D261" t="s">
+        <v>13</v>
+      </c>
+      <c r="E261" t="s">
+        <v>19</v>
+      </c>
+      <c r="F261" t="s">
+        <v>30</v>
+      </c>
+      <c r="G261">
+        <v>2660</v>
+      </c>
+    </row>
+    <row r="262" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A262">
+        <v>2026</v>
+      </c>
+      <c r="B262" t="s">
+        <v>49</v>
+      </c>
+      <c r="C262">
+        <v>10</v>
+      </c>
+      <c r="D262" t="s">
+        <v>14</v>
+      </c>
+      <c r="E262" t="s">
+        <v>19</v>
+      </c>
+      <c r="F262" t="s">
+        <v>31</v>
+      </c>
+      <c r="G262">
+        <v>3294</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A263">
+        <v>2026</v>
+      </c>
+      <c r="B263" t="s">
+        <v>49</v>
+      </c>
+      <c r="C263">
+        <v>10</v>
+      </c>
+      <c r="D263" t="s">
+        <v>14</v>
+      </c>
+      <c r="E263" t="s">
+        <v>19</v>
+      </c>
+      <c r="F263" t="s">
+        <v>32</v>
+      </c>
+      <c r="G263">
+        <v>10365</v>
+      </c>
+    </row>
+    <row r="264" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A264">
+        <v>2026</v>
+      </c>
+      <c r="B264" t="s">
+        <v>49</v>
+      </c>
+      <c r="C264">
+        <v>10</v>
+      </c>
+      <c r="D264" t="s">
+        <v>14</v>
+      </c>
+      <c r="E264" t="s">
+        <v>19</v>
+      </c>
+      <c r="F264" t="s">
+        <v>33</v>
+      </c>
+      <c r="G264">
+        <v>5642</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A265">
+        <v>2026</v>
+      </c>
+      <c r="B265" t="s">
+        <v>49</v>
+      </c>
+      <c r="C265">
+        <v>10</v>
+      </c>
+      <c r="D265" t="s">
+        <v>15</v>
+      </c>
+      <c r="E265" t="s">
+        <v>19</v>
+      </c>
+      <c r="F265" t="s">
+        <v>34</v>
+      </c>
+      <c r="G265">
+        <v>19712</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A266">
+        <v>2026</v>
+      </c>
+      <c r="B266" t="s">
+        <v>49</v>
+      </c>
+      <c r="C266">
+        <v>10</v>
+      </c>
+      <c r="D266" t="s">
+        <v>15</v>
+      </c>
+      <c r="E266" t="s">
+        <v>19</v>
+      </c>
+      <c r="F266" t="s">
+        <v>35</v>
+      </c>
+      <c r="G266">
+        <v>7150</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A267">
+        <v>2026</v>
+      </c>
+      <c r="B267" t="s">
+        <v>49</v>
+      </c>
+      <c r="C267">
+        <v>10</v>
+      </c>
+      <c r="D267" t="s">
+        <v>16</v>
+      </c>
+      <c r="E267" t="s">
+        <v>19</v>
+      </c>
+      <c r="F267" t="s">
+        <v>36</v>
+      </c>
+      <c r="G267">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A268">
+        <v>2026</v>
+      </c>
+      <c r="B268" t="s">
+        <v>49</v>
+      </c>
+      <c r="C268">
+        <v>10</v>
+      </c>
+      <c r="D268" t="s">
+        <v>16</v>
+      </c>
+      <c r="E268" t="s">
+        <v>19</v>
+      </c>
+      <c r="F268" t="s">
+        <v>37</v>
+      </c>
+      <c r="G268">
+        <v>3045</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A269">
+        <v>2026</v>
+      </c>
+      <c r="B269" t="s">
+        <v>49</v>
+      </c>
+      <c r="C269">
+        <v>10</v>
+      </c>
+      <c r="D269" t="s">
+        <v>16</v>
+      </c>
+      <c r="E269" t="s">
+        <v>19</v>
+      </c>
+      <c r="F269" t="s">
+        <v>38</v>
+      </c>
+      <c r="G269">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A270">
+        <v>2026</v>
+      </c>
+      <c r="B270" t="s">
+        <v>49</v>
+      </c>
+      <c r="C270">
+        <v>10</v>
+      </c>
+      <c r="D270" t="s">
+        <v>16</v>
+      </c>
+      <c r="E270" t="s">
+        <v>19</v>
+      </c>
+      <c r="F270" t="s">
+        <v>39</v>
+      </c>
+      <c r="G270">
+        <v>18871</v>
+      </c>
+    </row>
+    <row r="271" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A271">
+        <v>2026</v>
+      </c>
+      <c r="B271" t="s">
+        <v>49</v>
+      </c>
+      <c r="C271">
+        <v>10</v>
+      </c>
+      <c r="D271" t="s">
+        <v>17</v>
+      </c>
+      <c r="E271" t="s">
+        <v>17</v>
+      </c>
+      <c r="F271" t="s">
+        <v>40</v>
+      </c>
+      <c r="G271">
+        <v>89183</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A272">
+        <v>2026</v>
+      </c>
+      <c r="B272" t="s">
+        <v>49</v>
+      </c>
+      <c r="C272">
+        <v>10</v>
+      </c>
+      <c r="D272" t="s">
+        <v>18</v>
+      </c>
+      <c r="E272" t="s">
+        <v>19</v>
+      </c>
+      <c r="F272" t="s">
+        <v>41</v>
+      </c>
+      <c r="G272">
+        <v>2512</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A273">
+        <v>2026</v>
+      </c>
+      <c r="B273" t="s">
+        <v>49</v>
+      </c>
+      <c r="C273">
+        <v>10</v>
+      </c>
+      <c r="D273" t="s">
+        <v>18</v>
+      </c>
+      <c r="E273" t="s">
+        <v>19</v>
+      </c>
+      <c r="F273" t="s">
+        <v>42</v>
+      </c>
+      <c r="G273">
+        <v>13604</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A274">
+        <v>2026</v>
+      </c>
+      <c r="B274" t="s">
+        <v>49</v>
+      </c>
+      <c r="C274">
+        <v>10</v>
+      </c>
+      <c r="D274" t="s">
+        <v>18</v>
+      </c>
+      <c r="E274" t="s">
+        <v>19</v>
+      </c>
+      <c r="F274" t="s">
+        <v>43</v>
+      </c>
+      <c r="G274">
+        <v>2140</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A275">
+        <v>2026</v>
+      </c>
+      <c r="B275" t="s">
+        <v>49</v>
+      </c>
+      <c r="C275">
+        <v>10</v>
+      </c>
+      <c r="D275" t="s">
+        <v>18</v>
+      </c>
+      <c r="E275" t="s">
+        <v>19</v>
+      </c>
+      <c r="F275" t="s">
+        <v>45</v>
+      </c>
+      <c r="G275">
+        <v>9670</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A276">
+        <v>2026</v>
+      </c>
+      <c r="B276" t="s">
+        <v>49</v>
+      </c>
+      <c r="C276">
+        <v>10</v>
+      </c>
+      <c r="D276" t="s">
+        <v>18</v>
+      </c>
+      <c r="E276" t="s">
+        <v>19</v>
+      </c>
+      <c r="F276" t="s">
+        <v>46</v>
+      </c>
+      <c r="G276">
+        <v>7415</v>
+      </c>
+    </row>
     <row r="771" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G771" s="2"/>
     </row>

--- a/datos_reales.xlsx
+++ b/datos_reales.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acfestadistica\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61ED7530-F906-4CBA-8270-CCFBED232F8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7548A306-CCD3-4EDF-8ACC-8F2AEA84DEB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1107" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1219" uniqueCount="50">
   <si>
     <t>AÑO</t>
   </si>
@@ -6921,6 +6921,650 @@
         <v>7415</v>
       </c>
     </row>
+    <row r="277" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A277">
+        <v>2026</v>
+      </c>
+      <c r="B277" t="s">
+        <v>49</v>
+      </c>
+      <c r="C277">
+        <v>11</v>
+      </c>
+      <c r="D277" t="s">
+        <v>8</v>
+      </c>
+      <c r="E277" t="s">
+        <v>19</v>
+      </c>
+      <c r="F277" t="s">
+        <v>20</v>
+      </c>
+      <c r="G277">
+        <v>7245</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A278">
+        <v>2026</v>
+      </c>
+      <c r="B278" t="s">
+        <v>49</v>
+      </c>
+      <c r="C278">
+        <v>11</v>
+      </c>
+      <c r="D278" t="s">
+        <v>8</v>
+      </c>
+      <c r="E278" t="s">
+        <v>19</v>
+      </c>
+      <c r="F278" t="s">
+        <v>21</v>
+      </c>
+      <c r="G278">
+        <v>9875</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A279">
+        <v>2026</v>
+      </c>
+      <c r="B279" t="s">
+        <v>49</v>
+      </c>
+      <c r="C279">
+        <v>11</v>
+      </c>
+      <c r="D279" t="s">
+        <v>8</v>
+      </c>
+      <c r="E279" t="s">
+        <v>19</v>
+      </c>
+      <c r="F279" t="s">
+        <v>22</v>
+      </c>
+      <c r="G279">
+        <v>4115</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A280">
+        <v>2026</v>
+      </c>
+      <c r="B280" t="s">
+        <v>49</v>
+      </c>
+      <c r="C280">
+        <v>11</v>
+      </c>
+      <c r="D280" t="s">
+        <v>8</v>
+      </c>
+      <c r="E280" t="s">
+        <v>19</v>
+      </c>
+      <c r="F280" t="s">
+        <v>47</v>
+      </c>
+      <c r="G280">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A281">
+        <v>2026</v>
+      </c>
+      <c r="B281" t="s">
+        <v>49</v>
+      </c>
+      <c r="C281">
+        <v>11</v>
+      </c>
+      <c r="D281" t="s">
+        <v>9</v>
+      </c>
+      <c r="E281" t="s">
+        <v>19</v>
+      </c>
+      <c r="F281" t="s">
+        <v>23</v>
+      </c>
+      <c r="G281">
+        <v>1490</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A282">
+        <v>2026</v>
+      </c>
+      <c r="B282" t="s">
+        <v>49</v>
+      </c>
+      <c r="C282">
+        <v>11</v>
+      </c>
+      <c r="D282" t="s">
+        <v>11</v>
+      </c>
+      <c r="E282" t="s">
+        <v>19</v>
+      </c>
+      <c r="F282" t="s">
+        <v>25</v>
+      </c>
+      <c r="G282">
+        <v>2632</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A283">
+        <v>2026</v>
+      </c>
+      <c r="B283" t="s">
+        <v>49</v>
+      </c>
+      <c r="C283">
+        <v>11</v>
+      </c>
+      <c r="D283" t="s">
+        <v>11</v>
+      </c>
+      <c r="E283" t="s">
+        <v>19</v>
+      </c>
+      <c r="F283" t="s">
+        <v>24</v>
+      </c>
+      <c r="G283">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A284">
+        <v>2026</v>
+      </c>
+      <c r="B284" t="s">
+        <v>49</v>
+      </c>
+      <c r="C284">
+        <v>11</v>
+      </c>
+      <c r="D284" t="s">
+        <v>12</v>
+      </c>
+      <c r="E284" t="s">
+        <v>19</v>
+      </c>
+      <c r="F284" t="s">
+        <v>26</v>
+      </c>
+      <c r="G284">
+        <v>17620</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A285">
+        <v>2026</v>
+      </c>
+      <c r="B285" t="s">
+        <v>49</v>
+      </c>
+      <c r="C285">
+        <v>11</v>
+      </c>
+      <c r="D285" t="s">
+        <v>12</v>
+      </c>
+      <c r="E285" t="s">
+        <v>19</v>
+      </c>
+      <c r="F285" t="s">
+        <v>27</v>
+      </c>
+      <c r="G285">
+        <v>4362</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A286">
+        <v>2026</v>
+      </c>
+      <c r="B286" t="s">
+        <v>49</v>
+      </c>
+      <c r="C286">
+        <v>11</v>
+      </c>
+      <c r="D286" t="s">
+        <v>12</v>
+      </c>
+      <c r="E286" t="s">
+        <v>19</v>
+      </c>
+      <c r="F286" t="s">
+        <v>28</v>
+      </c>
+      <c r="G286">
+        <v>10307</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A287">
+        <v>2026</v>
+      </c>
+      <c r="B287" t="s">
+        <v>49</v>
+      </c>
+      <c r="C287">
+        <v>11</v>
+      </c>
+      <c r="D287" t="s">
+        <v>12</v>
+      </c>
+      <c r="E287" t="s">
+        <v>19</v>
+      </c>
+      <c r="F287" t="s">
+        <v>29</v>
+      </c>
+      <c r="G287">
+        <v>5657</v>
+      </c>
+    </row>
+    <row r="288" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A288">
+        <v>2026</v>
+      </c>
+      <c r="B288" t="s">
+        <v>49</v>
+      </c>
+      <c r="C288">
+        <v>11</v>
+      </c>
+      <c r="D288" t="s">
+        <v>13</v>
+      </c>
+      <c r="E288" t="s">
+        <v>19</v>
+      </c>
+      <c r="F288" t="s">
+        <v>30</v>
+      </c>
+      <c r="G288">
+        <v>2275</v>
+      </c>
+    </row>
+    <row r="289" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A289">
+        <v>2026</v>
+      </c>
+      <c r="B289" t="s">
+        <v>49</v>
+      </c>
+      <c r="C289">
+        <v>11</v>
+      </c>
+      <c r="D289" t="s">
+        <v>14</v>
+      </c>
+      <c r="E289" t="s">
+        <v>19</v>
+      </c>
+      <c r="F289" t="s">
+        <v>31</v>
+      </c>
+      <c r="G289">
+        <v>2060</v>
+      </c>
+    </row>
+    <row r="290" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A290">
+        <v>2026</v>
+      </c>
+      <c r="B290" t="s">
+        <v>49</v>
+      </c>
+      <c r="C290">
+        <v>11</v>
+      </c>
+      <c r="D290" t="s">
+        <v>14</v>
+      </c>
+      <c r="E290" t="s">
+        <v>19</v>
+      </c>
+      <c r="F290" t="s">
+        <v>32</v>
+      </c>
+      <c r="G290">
+        <v>9194</v>
+      </c>
+    </row>
+    <row r="291" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A291">
+        <v>2026</v>
+      </c>
+      <c r="B291" t="s">
+        <v>49</v>
+      </c>
+      <c r="C291">
+        <v>11</v>
+      </c>
+      <c r="D291" t="s">
+        <v>14</v>
+      </c>
+      <c r="E291" t="s">
+        <v>19</v>
+      </c>
+      <c r="F291" t="s">
+        <v>33</v>
+      </c>
+      <c r="G291">
+        <v>6255</v>
+      </c>
+    </row>
+    <row r="292" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A292">
+        <v>2026</v>
+      </c>
+      <c r="B292" t="s">
+        <v>49</v>
+      </c>
+      <c r="C292">
+        <v>11</v>
+      </c>
+      <c r="D292" t="s">
+        <v>15</v>
+      </c>
+      <c r="E292" t="s">
+        <v>19</v>
+      </c>
+      <c r="F292" t="s">
+        <v>34</v>
+      </c>
+      <c r="G292">
+        <v>13890</v>
+      </c>
+    </row>
+    <row r="293" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A293">
+        <v>2026</v>
+      </c>
+      <c r="B293" t="s">
+        <v>49</v>
+      </c>
+      <c r="C293">
+        <v>11</v>
+      </c>
+      <c r="D293" t="s">
+        <v>15</v>
+      </c>
+      <c r="E293" t="s">
+        <v>19</v>
+      </c>
+      <c r="F293" t="s">
+        <v>35</v>
+      </c>
+      <c r="G293">
+        <v>7080</v>
+      </c>
+    </row>
+    <row r="294" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A294">
+        <v>2026</v>
+      </c>
+      <c r="B294" t="s">
+        <v>49</v>
+      </c>
+      <c r="C294">
+        <v>11</v>
+      </c>
+      <c r="D294" t="s">
+        <v>16</v>
+      </c>
+      <c r="E294" t="s">
+        <v>19</v>
+      </c>
+      <c r="F294" t="s">
+        <v>36</v>
+      </c>
+      <c r="G294">
+        <v>2143</v>
+      </c>
+    </row>
+    <row r="295" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A295">
+        <v>2026</v>
+      </c>
+      <c r="B295" t="s">
+        <v>49</v>
+      </c>
+      <c r="C295">
+        <v>11</v>
+      </c>
+      <c r="D295" t="s">
+        <v>16</v>
+      </c>
+      <c r="E295" t="s">
+        <v>19</v>
+      </c>
+      <c r="F295" t="s">
+        <v>37</v>
+      </c>
+      <c r="G295">
+        <v>2304</v>
+      </c>
+    </row>
+    <row r="296" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A296">
+        <v>2026</v>
+      </c>
+      <c r="B296" t="s">
+        <v>49</v>
+      </c>
+      <c r="C296">
+        <v>11</v>
+      </c>
+      <c r="D296" t="s">
+        <v>16</v>
+      </c>
+      <c r="E296" t="s">
+        <v>19</v>
+      </c>
+      <c r="F296" t="s">
+        <v>38</v>
+      </c>
+      <c r="G296">
+        <v>1360</v>
+      </c>
+    </row>
+    <row r="297" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A297">
+        <v>2026</v>
+      </c>
+      <c r="B297" t="s">
+        <v>49</v>
+      </c>
+      <c r="C297">
+        <v>11</v>
+      </c>
+      <c r="D297" t="s">
+        <v>16</v>
+      </c>
+      <c r="E297" t="s">
+        <v>19</v>
+      </c>
+      <c r="F297" t="s">
+        <v>39</v>
+      </c>
+      <c r="G297">
+        <v>15760</v>
+      </c>
+    </row>
+    <row r="298" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A298">
+        <v>2026</v>
+      </c>
+      <c r="B298" t="s">
+        <v>49</v>
+      </c>
+      <c r="C298">
+        <v>11</v>
+      </c>
+      <c r="D298" t="s">
+        <v>17</v>
+      </c>
+      <c r="E298" t="s">
+        <v>17</v>
+      </c>
+      <c r="F298" t="s">
+        <v>40</v>
+      </c>
+      <c r="G298">
+        <v>79398</v>
+      </c>
+    </row>
+    <row r="299" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A299">
+        <v>2026</v>
+      </c>
+      <c r="B299" t="s">
+        <v>49</v>
+      </c>
+      <c r="C299">
+        <v>11</v>
+      </c>
+      <c r="D299" t="s">
+        <v>18</v>
+      </c>
+      <c r="E299" t="s">
+        <v>19</v>
+      </c>
+      <c r="F299" t="s">
+        <v>41</v>
+      </c>
+      <c r="G299">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="300" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A300">
+        <v>2026</v>
+      </c>
+      <c r="B300" t="s">
+        <v>49</v>
+      </c>
+      <c r="C300">
+        <v>11</v>
+      </c>
+      <c r="D300" t="s">
+        <v>18</v>
+      </c>
+      <c r="E300" t="s">
+        <v>19</v>
+      </c>
+      <c r="F300" t="s">
+        <v>42</v>
+      </c>
+      <c r="G300">
+        <v>12819</v>
+      </c>
+    </row>
+    <row r="301" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A301">
+        <v>2026</v>
+      </c>
+      <c r="B301" t="s">
+        <v>49</v>
+      </c>
+      <c r="C301">
+        <v>11</v>
+      </c>
+      <c r="D301" t="s">
+        <v>18</v>
+      </c>
+      <c r="E301" t="s">
+        <v>19</v>
+      </c>
+      <c r="F301" t="s">
+        <v>43</v>
+      </c>
+      <c r="G301">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="302" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A302">
+        <v>2026</v>
+      </c>
+      <c r="B302" t="s">
+        <v>49</v>
+      </c>
+      <c r="C302">
+        <v>11</v>
+      </c>
+      <c r="D302" t="s">
+        <v>18</v>
+      </c>
+      <c r="E302" t="s">
+        <v>19</v>
+      </c>
+      <c r="F302" t="s">
+        <v>44</v>
+      </c>
+      <c r="G302">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="303" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A303">
+        <v>2026</v>
+      </c>
+      <c r="B303" t="s">
+        <v>49</v>
+      </c>
+      <c r="C303">
+        <v>11</v>
+      </c>
+      <c r="D303" t="s">
+        <v>18</v>
+      </c>
+      <c r="E303" t="s">
+        <v>19</v>
+      </c>
+      <c r="F303" t="s">
+        <v>45</v>
+      </c>
+      <c r="G303">
+        <v>7881</v>
+      </c>
+    </row>
+    <row r="304" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A304">
+        <v>2026</v>
+      </c>
+      <c r="B304" t="s">
+        <v>49</v>
+      </c>
+      <c r="C304">
+        <v>11</v>
+      </c>
+      <c r="D304" t="s">
+        <v>18</v>
+      </c>
+      <c r="E304" t="s">
+        <v>19</v>
+      </c>
+      <c r="F304" t="s">
+        <v>46</v>
+      </c>
+      <c r="G304">
+        <v>6713</v>
+      </c>
+    </row>
     <row r="771" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G771" s="2"/>
     </row>

--- a/datos_reales.xlsx
+++ b/datos_reales.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acfestadistica\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7548A306-CCD3-4EDF-8ACC-8F2AEA84DEB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2682701-1E71-47E6-A95E-68FC75B772F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1219" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1335" uniqueCount="51">
   <si>
     <t>AÑO</t>
   </si>
@@ -187,6 +187,9 @@
   <si>
     <t>MARZO</t>
   </si>
+  <si>
+    <t>REDVOLUTION</t>
+  </si>
 </sst>
 </file>
 
@@ -256,13 +259,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7565,6 +7569,673 @@
         <v>6713</v>
       </c>
     </row>
+    <row r="305" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A305">
+        <v>2026</v>
+      </c>
+      <c r="B305" t="s">
+        <v>49</v>
+      </c>
+      <c r="C305">
+        <v>12</v>
+      </c>
+      <c r="D305" t="s">
+        <v>8</v>
+      </c>
+      <c r="E305" t="s">
+        <v>19</v>
+      </c>
+      <c r="F305" t="s">
+        <v>20</v>
+      </c>
+      <c r="G305" s="4">
+        <v>6310</v>
+      </c>
+    </row>
+    <row r="306" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A306">
+        <v>2026</v>
+      </c>
+      <c r="B306" t="s">
+        <v>49</v>
+      </c>
+      <c r="C306">
+        <v>12</v>
+      </c>
+      <c r="D306" t="s">
+        <v>8</v>
+      </c>
+      <c r="E306" t="s">
+        <v>19</v>
+      </c>
+      <c r="F306" t="s">
+        <v>21</v>
+      </c>
+      <c r="G306" s="4">
+        <v>10080</v>
+      </c>
+    </row>
+    <row r="307" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A307">
+        <v>2026</v>
+      </c>
+      <c r="B307" t="s">
+        <v>49</v>
+      </c>
+      <c r="C307">
+        <v>12</v>
+      </c>
+      <c r="D307" t="s">
+        <v>8</v>
+      </c>
+      <c r="E307" t="s">
+        <v>19</v>
+      </c>
+      <c r="F307" t="s">
+        <v>22</v>
+      </c>
+      <c r="G307" s="4">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="308" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A308">
+        <v>2026</v>
+      </c>
+      <c r="B308" t="s">
+        <v>49</v>
+      </c>
+      <c r="C308">
+        <v>12</v>
+      </c>
+      <c r="D308" t="s">
+        <v>8</v>
+      </c>
+      <c r="E308" t="s">
+        <v>19</v>
+      </c>
+      <c r="F308" t="s">
+        <v>47</v>
+      </c>
+      <c r="G308">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="309" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A309">
+        <v>2026</v>
+      </c>
+      <c r="B309" t="s">
+        <v>49</v>
+      </c>
+      <c r="C309">
+        <v>12</v>
+      </c>
+      <c r="D309" t="s">
+        <v>9</v>
+      </c>
+      <c r="E309" t="s">
+        <v>19</v>
+      </c>
+      <c r="F309" t="s">
+        <v>23</v>
+      </c>
+      <c r="G309" s="4">
+        <v>1709</v>
+      </c>
+    </row>
+    <row r="310" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A310">
+        <v>2026</v>
+      </c>
+      <c r="B310" t="s">
+        <v>49</v>
+      </c>
+      <c r="C310">
+        <v>12</v>
+      </c>
+      <c r="D310" t="s">
+        <v>11</v>
+      </c>
+      <c r="E310" t="s">
+        <v>19</v>
+      </c>
+      <c r="F310" t="s">
+        <v>25</v>
+      </c>
+      <c r="G310" s="4">
+        <v>2720</v>
+      </c>
+    </row>
+    <row r="311" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A311">
+        <v>2026</v>
+      </c>
+      <c r="B311" t="s">
+        <v>49</v>
+      </c>
+      <c r="C311">
+        <v>12</v>
+      </c>
+      <c r="D311" t="s">
+        <v>11</v>
+      </c>
+      <c r="E311" t="s">
+        <v>19</v>
+      </c>
+      <c r="F311" t="s">
+        <v>24</v>
+      </c>
+      <c r="G311">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="312" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A312">
+        <v>2026</v>
+      </c>
+      <c r="B312" t="s">
+        <v>49</v>
+      </c>
+      <c r="C312">
+        <v>12</v>
+      </c>
+      <c r="D312" t="s">
+        <v>12</v>
+      </c>
+      <c r="E312" t="s">
+        <v>19</v>
+      </c>
+      <c r="F312" t="s">
+        <v>26</v>
+      </c>
+      <c r="G312" s="4">
+        <v>15450</v>
+      </c>
+    </row>
+    <row r="313" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A313">
+        <v>2026</v>
+      </c>
+      <c r="B313" t="s">
+        <v>49</v>
+      </c>
+      <c r="C313">
+        <v>12</v>
+      </c>
+      <c r="D313" t="s">
+        <v>12</v>
+      </c>
+      <c r="E313" t="s">
+        <v>19</v>
+      </c>
+      <c r="F313" t="s">
+        <v>27</v>
+      </c>
+      <c r="G313" s="4">
+        <v>5955</v>
+      </c>
+    </row>
+    <row r="314" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A314">
+        <v>2026</v>
+      </c>
+      <c r="B314" t="s">
+        <v>49</v>
+      </c>
+      <c r="C314">
+        <v>12</v>
+      </c>
+      <c r="D314" t="s">
+        <v>12</v>
+      </c>
+      <c r="E314" t="s">
+        <v>19</v>
+      </c>
+      <c r="F314" t="s">
+        <v>28</v>
+      </c>
+      <c r="G314" s="4">
+        <v>6825</v>
+      </c>
+    </row>
+    <row r="315" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A315">
+        <v>2026</v>
+      </c>
+      <c r="B315" t="s">
+        <v>49</v>
+      </c>
+      <c r="C315">
+        <v>12</v>
+      </c>
+      <c r="D315" t="s">
+        <v>12</v>
+      </c>
+      <c r="E315" t="s">
+        <v>19</v>
+      </c>
+      <c r="F315" t="s">
+        <v>29</v>
+      </c>
+      <c r="G315" s="4">
+        <v>6360</v>
+      </c>
+    </row>
+    <row r="316" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A316">
+        <v>2026</v>
+      </c>
+      <c r="B316" t="s">
+        <v>49</v>
+      </c>
+      <c r="C316">
+        <v>12</v>
+      </c>
+      <c r="D316" t="s">
+        <v>13</v>
+      </c>
+      <c r="E316" t="s">
+        <v>19</v>
+      </c>
+      <c r="F316" t="s">
+        <v>30</v>
+      </c>
+      <c r="G316" s="4">
+        <v>3350</v>
+      </c>
+    </row>
+    <row r="317" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A317">
+        <v>2026</v>
+      </c>
+      <c r="B317" t="s">
+        <v>49</v>
+      </c>
+      <c r="C317">
+        <v>12</v>
+      </c>
+      <c r="D317" t="s">
+        <v>14</v>
+      </c>
+      <c r="E317" t="s">
+        <v>19</v>
+      </c>
+      <c r="F317" t="s">
+        <v>31</v>
+      </c>
+      <c r="G317" s="4">
+        <v>2670</v>
+      </c>
+    </row>
+    <row r="318" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A318">
+        <v>2026</v>
+      </c>
+      <c r="B318" t="s">
+        <v>49</v>
+      </c>
+      <c r="C318">
+        <v>12</v>
+      </c>
+      <c r="D318" t="s">
+        <v>14</v>
+      </c>
+      <c r="E318" t="s">
+        <v>19</v>
+      </c>
+      <c r="F318" t="s">
+        <v>32</v>
+      </c>
+      <c r="G318" s="4">
+        <v>11330</v>
+      </c>
+    </row>
+    <row r="319" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A319">
+        <v>2026</v>
+      </c>
+      <c r="B319" t="s">
+        <v>49</v>
+      </c>
+      <c r="C319">
+        <v>12</v>
+      </c>
+      <c r="D319" t="s">
+        <v>14</v>
+      </c>
+      <c r="E319" t="s">
+        <v>19</v>
+      </c>
+      <c r="F319" t="s">
+        <v>33</v>
+      </c>
+      <c r="G319" s="4">
+        <v>7133</v>
+      </c>
+    </row>
+    <row r="320" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A320">
+        <v>2026</v>
+      </c>
+      <c r="B320" t="s">
+        <v>49</v>
+      </c>
+      <c r="C320">
+        <v>12</v>
+      </c>
+      <c r="D320" t="s">
+        <v>15</v>
+      </c>
+      <c r="E320" t="s">
+        <v>19</v>
+      </c>
+      <c r="F320" t="s">
+        <v>34</v>
+      </c>
+      <c r="G320" s="4">
+        <v>12750</v>
+      </c>
+    </row>
+    <row r="321" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A321">
+        <v>2026</v>
+      </c>
+      <c r="B321" t="s">
+        <v>49</v>
+      </c>
+      <c r="C321">
+        <v>12</v>
+      </c>
+      <c r="D321" t="s">
+        <v>15</v>
+      </c>
+      <c r="E321" t="s">
+        <v>19</v>
+      </c>
+      <c r="F321" t="s">
+        <v>35</v>
+      </c>
+      <c r="G321" s="4">
+        <v>8806</v>
+      </c>
+    </row>
+    <row r="322" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A322">
+        <v>2026</v>
+      </c>
+      <c r="B322" t="s">
+        <v>49</v>
+      </c>
+      <c r="C322">
+        <v>12</v>
+      </c>
+      <c r="D322" t="s">
+        <v>16</v>
+      </c>
+      <c r="E322" t="s">
+        <v>19</v>
+      </c>
+      <c r="F322" t="s">
+        <v>36</v>
+      </c>
+      <c r="G322" s="4">
+        <v>2420</v>
+      </c>
+    </row>
+    <row r="323" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A323">
+        <v>2026</v>
+      </c>
+      <c r="B323" t="s">
+        <v>49</v>
+      </c>
+      <c r="C323">
+        <v>12</v>
+      </c>
+      <c r="D323" t="s">
+        <v>16</v>
+      </c>
+      <c r="E323" t="s">
+        <v>19</v>
+      </c>
+      <c r="F323" t="s">
+        <v>37</v>
+      </c>
+      <c r="G323" s="4">
+        <v>2482</v>
+      </c>
+    </row>
+    <row r="324" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A324">
+        <v>2026</v>
+      </c>
+      <c r="B324" t="s">
+        <v>49</v>
+      </c>
+      <c r="C324">
+        <v>12</v>
+      </c>
+      <c r="D324" t="s">
+        <v>16</v>
+      </c>
+      <c r="E324" t="s">
+        <v>19</v>
+      </c>
+      <c r="F324" t="s">
+        <v>38</v>
+      </c>
+      <c r="G324" s="4">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="325" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A325">
+        <v>2026</v>
+      </c>
+      <c r="B325" t="s">
+        <v>49</v>
+      </c>
+      <c r="C325">
+        <v>12</v>
+      </c>
+      <c r="D325" t="s">
+        <v>16</v>
+      </c>
+      <c r="E325" t="s">
+        <v>19</v>
+      </c>
+      <c r="F325" t="s">
+        <v>39</v>
+      </c>
+      <c r="G325" s="4">
+        <v>17186</v>
+      </c>
+    </row>
+    <row r="326" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A326">
+        <v>2026</v>
+      </c>
+      <c r="B326" t="s">
+        <v>49</v>
+      </c>
+      <c r="C326">
+        <v>12</v>
+      </c>
+      <c r="D326" t="s">
+        <v>17</v>
+      </c>
+      <c r="E326" t="s">
+        <v>17</v>
+      </c>
+      <c r="F326" t="s">
+        <v>40</v>
+      </c>
+      <c r="G326" s="4">
+        <v>76121</v>
+      </c>
+    </row>
+    <row r="327" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A327">
+        <v>2026</v>
+      </c>
+      <c r="B327" t="s">
+        <v>49</v>
+      </c>
+      <c r="C327">
+        <v>12</v>
+      </c>
+      <c r="D327" t="s">
+        <v>17</v>
+      </c>
+      <c r="E327" t="s">
+        <v>17</v>
+      </c>
+      <c r="F327" t="s">
+        <v>50</v>
+      </c>
+      <c r="G327">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="328" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A328">
+        <v>2026</v>
+      </c>
+      <c r="B328" t="s">
+        <v>49</v>
+      </c>
+      <c r="C328">
+        <v>12</v>
+      </c>
+      <c r="D328" t="s">
+        <v>18</v>
+      </c>
+      <c r="E328" t="s">
+        <v>19</v>
+      </c>
+      <c r="F328" t="s">
+        <v>41</v>
+      </c>
+      <c r="G328" s="4">
+        <v>5410</v>
+      </c>
+    </row>
+    <row r="329" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A329">
+        <v>2026</v>
+      </c>
+      <c r="B329" t="s">
+        <v>49</v>
+      </c>
+      <c r="C329">
+        <v>12</v>
+      </c>
+      <c r="D329" t="s">
+        <v>18</v>
+      </c>
+      <c r="E329" t="s">
+        <v>19</v>
+      </c>
+      <c r="F329" t="s">
+        <v>42</v>
+      </c>
+      <c r="G329" s="4">
+        <v>13965</v>
+      </c>
+    </row>
+    <row r="330" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A330">
+        <v>2026</v>
+      </c>
+      <c r="B330" t="s">
+        <v>49</v>
+      </c>
+      <c r="C330">
+        <v>12</v>
+      </c>
+      <c r="D330" t="s">
+        <v>18</v>
+      </c>
+      <c r="E330" t="s">
+        <v>19</v>
+      </c>
+      <c r="F330" t="s">
+        <v>43</v>
+      </c>
+      <c r="G330" s="4">
+        <v>1614</v>
+      </c>
+    </row>
+    <row r="331" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A331">
+        <v>2026</v>
+      </c>
+      <c r="B331" t="s">
+        <v>49</v>
+      </c>
+      <c r="C331">
+        <v>12</v>
+      </c>
+      <c r="D331" t="s">
+        <v>18</v>
+      </c>
+      <c r="E331" t="s">
+        <v>19</v>
+      </c>
+      <c r="F331" t="s">
+        <v>44</v>
+      </c>
+      <c r="G331">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="332" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A332">
+        <v>2026</v>
+      </c>
+      <c r="B332" t="s">
+        <v>49</v>
+      </c>
+      <c r="C332">
+        <v>12</v>
+      </c>
+      <c r="D332" t="s">
+        <v>18</v>
+      </c>
+      <c r="E332" t="s">
+        <v>19</v>
+      </c>
+      <c r="F332" t="s">
+        <v>45</v>
+      </c>
+      <c r="G332" s="4">
+        <v>6037</v>
+      </c>
+    </row>
+    <row r="333" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A333">
+        <v>2026</v>
+      </c>
+      <c r="B333" t="s">
+        <v>49</v>
+      </c>
+      <c r="C333">
+        <v>12</v>
+      </c>
+      <c r="D333" t="s">
+        <v>18</v>
+      </c>
+      <c r="E333" t="s">
+        <v>19</v>
+      </c>
+      <c r="F333" t="s">
+        <v>46</v>
+      </c>
+      <c r="G333" s="4">
+        <v>7305</v>
+      </c>
+    </row>
     <row r="771" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G771" s="2"/>
     </row>

--- a/datos_reales.xlsx
+++ b/datos_reales.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acfestadistica\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2682701-1E71-47E6-A95E-68FC75B772F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32AB9EE9-7E8F-486A-9731-5CE0F559C8EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1335" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1451" uniqueCount="51">
   <si>
     <t>AÑO</t>
   </si>
@@ -8236,6 +8236,673 @@
         <v>7305</v>
       </c>
     </row>
+    <row r="334" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A334">
+        <v>2026</v>
+      </c>
+      <c r="B334" t="s">
+        <v>49</v>
+      </c>
+      <c r="C334">
+        <v>13</v>
+      </c>
+      <c r="D334" t="s">
+        <v>8</v>
+      </c>
+      <c r="E334" t="s">
+        <v>19</v>
+      </c>
+      <c r="F334" t="s">
+        <v>20</v>
+      </c>
+      <c r="G334">
+        <v>6902</v>
+      </c>
+    </row>
+    <row r="335" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A335">
+        <v>2026</v>
+      </c>
+      <c r="B335" t="s">
+        <v>49</v>
+      </c>
+      <c r="C335">
+        <v>13</v>
+      </c>
+      <c r="D335" t="s">
+        <v>8</v>
+      </c>
+      <c r="E335" t="s">
+        <v>19</v>
+      </c>
+      <c r="F335" t="s">
+        <v>21</v>
+      </c>
+      <c r="G335">
+        <v>12454</v>
+      </c>
+    </row>
+    <row r="336" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A336">
+        <v>2026</v>
+      </c>
+      <c r="B336" t="s">
+        <v>49</v>
+      </c>
+      <c r="C336">
+        <v>13</v>
+      </c>
+      <c r="D336" t="s">
+        <v>8</v>
+      </c>
+      <c r="E336" t="s">
+        <v>19</v>
+      </c>
+      <c r="F336" t="s">
+        <v>22</v>
+      </c>
+      <c r="G336">
+        <v>4699</v>
+      </c>
+    </row>
+    <row r="337" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A337">
+        <v>2026</v>
+      </c>
+      <c r="B337" t="s">
+        <v>49</v>
+      </c>
+      <c r="C337">
+        <v>13</v>
+      </c>
+      <c r="D337" t="s">
+        <v>8</v>
+      </c>
+      <c r="E337" t="s">
+        <v>19</v>
+      </c>
+      <c r="F337" t="s">
+        <v>47</v>
+      </c>
+      <c r="G337">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="338" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A338">
+        <v>2026</v>
+      </c>
+      <c r="B338" t="s">
+        <v>49</v>
+      </c>
+      <c r="C338">
+        <v>13</v>
+      </c>
+      <c r="D338" t="s">
+        <v>9</v>
+      </c>
+      <c r="E338" t="s">
+        <v>19</v>
+      </c>
+      <c r="F338" t="s">
+        <v>23</v>
+      </c>
+      <c r="G338">
+        <v>2366</v>
+      </c>
+    </row>
+    <row r="339" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A339">
+        <v>2026</v>
+      </c>
+      <c r="B339" t="s">
+        <v>49</v>
+      </c>
+      <c r="C339">
+        <v>13</v>
+      </c>
+      <c r="D339" t="s">
+        <v>11</v>
+      </c>
+      <c r="E339" t="s">
+        <v>19</v>
+      </c>
+      <c r="F339" t="s">
+        <v>25</v>
+      </c>
+      <c r="G339">
+        <v>2960</v>
+      </c>
+    </row>
+    <row r="340" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A340">
+        <v>2026</v>
+      </c>
+      <c r="B340" t="s">
+        <v>49</v>
+      </c>
+      <c r="C340">
+        <v>13</v>
+      </c>
+      <c r="D340" t="s">
+        <v>11</v>
+      </c>
+      <c r="E340" t="s">
+        <v>19</v>
+      </c>
+      <c r="F340" t="s">
+        <v>24</v>
+      </c>
+      <c r="G340">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="341" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A341">
+        <v>2026</v>
+      </c>
+      <c r="B341" t="s">
+        <v>49</v>
+      </c>
+      <c r="C341">
+        <v>13</v>
+      </c>
+      <c r="D341" t="s">
+        <v>12</v>
+      </c>
+      <c r="E341" t="s">
+        <v>19</v>
+      </c>
+      <c r="F341" t="s">
+        <v>26</v>
+      </c>
+      <c r="G341">
+        <v>15563</v>
+      </c>
+    </row>
+    <row r="342" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A342">
+        <v>2026</v>
+      </c>
+      <c r="B342" t="s">
+        <v>49</v>
+      </c>
+      <c r="C342">
+        <v>13</v>
+      </c>
+      <c r="D342" t="s">
+        <v>12</v>
+      </c>
+      <c r="E342" t="s">
+        <v>19</v>
+      </c>
+      <c r="F342" t="s">
+        <v>27</v>
+      </c>
+      <c r="G342">
+        <v>4967</v>
+      </c>
+    </row>
+    <row r="343" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A343">
+        <v>2026</v>
+      </c>
+      <c r="B343" t="s">
+        <v>49</v>
+      </c>
+      <c r="C343">
+        <v>13</v>
+      </c>
+      <c r="D343" t="s">
+        <v>12</v>
+      </c>
+      <c r="E343" t="s">
+        <v>19</v>
+      </c>
+      <c r="F343" t="s">
+        <v>28</v>
+      </c>
+      <c r="G343">
+        <v>6532</v>
+      </c>
+    </row>
+    <row r="344" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A344">
+        <v>2026</v>
+      </c>
+      <c r="B344" t="s">
+        <v>49</v>
+      </c>
+      <c r="C344">
+        <v>13</v>
+      </c>
+      <c r="D344" t="s">
+        <v>12</v>
+      </c>
+      <c r="E344" t="s">
+        <v>19</v>
+      </c>
+      <c r="F344" t="s">
+        <v>29</v>
+      </c>
+      <c r="G344">
+        <v>6270</v>
+      </c>
+    </row>
+    <row r="345" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A345">
+        <v>2026</v>
+      </c>
+      <c r="B345" t="s">
+        <v>49</v>
+      </c>
+      <c r="C345">
+        <v>13</v>
+      </c>
+      <c r="D345" t="s">
+        <v>13</v>
+      </c>
+      <c r="E345" t="s">
+        <v>19</v>
+      </c>
+      <c r="F345" t="s">
+        <v>30</v>
+      </c>
+      <c r="G345">
+        <v>3572</v>
+      </c>
+    </row>
+    <row r="346" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A346">
+        <v>2026</v>
+      </c>
+      <c r="B346" t="s">
+        <v>49</v>
+      </c>
+      <c r="C346">
+        <v>13</v>
+      </c>
+      <c r="D346" t="s">
+        <v>14</v>
+      </c>
+      <c r="E346" t="s">
+        <v>19</v>
+      </c>
+      <c r="F346" t="s">
+        <v>31</v>
+      </c>
+      <c r="G346">
+        <v>3360</v>
+      </c>
+    </row>
+    <row r="347" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A347">
+        <v>2026</v>
+      </c>
+      <c r="B347" t="s">
+        <v>49</v>
+      </c>
+      <c r="C347">
+        <v>13</v>
+      </c>
+      <c r="D347" t="s">
+        <v>14</v>
+      </c>
+      <c r="E347" t="s">
+        <v>19</v>
+      </c>
+      <c r="F347" t="s">
+        <v>32</v>
+      </c>
+      <c r="G347">
+        <v>9825</v>
+      </c>
+    </row>
+    <row r="348" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A348">
+        <v>2026</v>
+      </c>
+      <c r="B348" t="s">
+        <v>49</v>
+      </c>
+      <c r="C348">
+        <v>13</v>
+      </c>
+      <c r="D348" t="s">
+        <v>14</v>
+      </c>
+      <c r="E348" t="s">
+        <v>19</v>
+      </c>
+      <c r="F348" t="s">
+        <v>33</v>
+      </c>
+      <c r="G348">
+        <v>8984</v>
+      </c>
+    </row>
+    <row r="349" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A349">
+        <v>2026</v>
+      </c>
+      <c r="B349" t="s">
+        <v>49</v>
+      </c>
+      <c r="C349">
+        <v>13</v>
+      </c>
+      <c r="D349" t="s">
+        <v>15</v>
+      </c>
+      <c r="E349" t="s">
+        <v>19</v>
+      </c>
+      <c r="F349" t="s">
+        <v>34</v>
+      </c>
+      <c r="G349">
+        <v>16850</v>
+      </c>
+    </row>
+    <row r="350" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A350">
+        <v>2026</v>
+      </c>
+      <c r="B350" t="s">
+        <v>49</v>
+      </c>
+      <c r="C350">
+        <v>13</v>
+      </c>
+      <c r="D350" t="s">
+        <v>15</v>
+      </c>
+      <c r="E350" t="s">
+        <v>19</v>
+      </c>
+      <c r="F350" t="s">
+        <v>35</v>
+      </c>
+      <c r="G350">
+        <v>9112</v>
+      </c>
+    </row>
+    <row r="351" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A351">
+        <v>2026</v>
+      </c>
+      <c r="B351" t="s">
+        <v>49</v>
+      </c>
+      <c r="C351">
+        <v>13</v>
+      </c>
+      <c r="D351" t="s">
+        <v>16</v>
+      </c>
+      <c r="E351" t="s">
+        <v>19</v>
+      </c>
+      <c r="F351" t="s">
+        <v>36</v>
+      </c>
+      <c r="G351">
+        <v>3275</v>
+      </c>
+    </row>
+    <row r="352" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A352">
+        <v>2026</v>
+      </c>
+      <c r="B352" t="s">
+        <v>49</v>
+      </c>
+      <c r="C352">
+        <v>13</v>
+      </c>
+      <c r="D352" t="s">
+        <v>16</v>
+      </c>
+      <c r="E352" t="s">
+        <v>19</v>
+      </c>
+      <c r="F352" t="s">
+        <v>37</v>
+      </c>
+      <c r="G352">
+        <v>2906</v>
+      </c>
+    </row>
+    <row r="353" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A353">
+        <v>2026</v>
+      </c>
+      <c r="B353" t="s">
+        <v>49</v>
+      </c>
+      <c r="C353">
+        <v>13</v>
+      </c>
+      <c r="D353" t="s">
+        <v>16</v>
+      </c>
+      <c r="E353" t="s">
+        <v>19</v>
+      </c>
+      <c r="F353" t="s">
+        <v>38</v>
+      </c>
+      <c r="G353">
+        <v>1833</v>
+      </c>
+    </row>
+    <row r="354" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A354">
+        <v>2026</v>
+      </c>
+      <c r="B354" t="s">
+        <v>49</v>
+      </c>
+      <c r="C354">
+        <v>13</v>
+      </c>
+      <c r="D354" t="s">
+        <v>16</v>
+      </c>
+      <c r="E354" t="s">
+        <v>19</v>
+      </c>
+      <c r="F354" t="s">
+        <v>39</v>
+      </c>
+      <c r="G354">
+        <v>18030</v>
+      </c>
+    </row>
+    <row r="355" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A355">
+        <v>2026</v>
+      </c>
+      <c r="B355" t="s">
+        <v>49</v>
+      </c>
+      <c r="C355">
+        <v>13</v>
+      </c>
+      <c r="D355" t="s">
+        <v>17</v>
+      </c>
+      <c r="E355" t="s">
+        <v>17</v>
+      </c>
+      <c r="F355" t="s">
+        <v>40</v>
+      </c>
+      <c r="G355">
+        <v>110852</v>
+      </c>
+    </row>
+    <row r="356" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A356">
+        <v>2026</v>
+      </c>
+      <c r="B356" t="s">
+        <v>49</v>
+      </c>
+      <c r="C356">
+        <v>13</v>
+      </c>
+      <c r="D356" t="s">
+        <v>17</v>
+      </c>
+      <c r="E356" t="s">
+        <v>17</v>
+      </c>
+      <c r="F356" t="s">
+        <v>50</v>
+      </c>
+      <c r="G356">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="357" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A357">
+        <v>2026</v>
+      </c>
+      <c r="B357" t="s">
+        <v>49</v>
+      </c>
+      <c r="C357">
+        <v>13</v>
+      </c>
+      <c r="D357" t="s">
+        <v>18</v>
+      </c>
+      <c r="E357" t="s">
+        <v>19</v>
+      </c>
+      <c r="F357" t="s">
+        <v>41</v>
+      </c>
+      <c r="G357">
+        <v>6670</v>
+      </c>
+    </row>
+    <row r="358" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A358">
+        <v>2026</v>
+      </c>
+      <c r="B358" t="s">
+        <v>49</v>
+      </c>
+      <c r="C358">
+        <v>13</v>
+      </c>
+      <c r="D358" t="s">
+        <v>18</v>
+      </c>
+      <c r="E358" t="s">
+        <v>19</v>
+      </c>
+      <c r="F358" t="s">
+        <v>42</v>
+      </c>
+      <c r="G358">
+        <v>16120</v>
+      </c>
+    </row>
+    <row r="359" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A359">
+        <v>2026</v>
+      </c>
+      <c r="B359" t="s">
+        <v>49</v>
+      </c>
+      <c r="C359">
+        <v>13</v>
+      </c>
+      <c r="D359" t="s">
+        <v>18</v>
+      </c>
+      <c r="E359" t="s">
+        <v>19</v>
+      </c>
+      <c r="F359" t="s">
+        <v>43</v>
+      </c>
+      <c r="G359">
+        <v>1920</v>
+      </c>
+    </row>
+    <row r="360" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A360">
+        <v>2026</v>
+      </c>
+      <c r="B360" t="s">
+        <v>49</v>
+      </c>
+      <c r="C360">
+        <v>13</v>
+      </c>
+      <c r="D360" t="s">
+        <v>18</v>
+      </c>
+      <c r="E360" t="s">
+        <v>19</v>
+      </c>
+      <c r="F360" t="s">
+        <v>44</v>
+      </c>
+      <c r="G360">
+        <v>3150</v>
+      </c>
+    </row>
+    <row r="361" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A361">
+        <v>2026</v>
+      </c>
+      <c r="B361" t="s">
+        <v>49</v>
+      </c>
+      <c r="C361">
+        <v>13</v>
+      </c>
+      <c r="D361" t="s">
+        <v>18</v>
+      </c>
+      <c r="E361" t="s">
+        <v>19</v>
+      </c>
+      <c r="F361" t="s">
+        <v>45</v>
+      </c>
+      <c r="G361">
+        <v>7045</v>
+      </c>
+    </row>
+    <row r="362" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A362">
+        <v>2026</v>
+      </c>
+      <c r="B362" t="s">
+        <v>49</v>
+      </c>
+      <c r="C362">
+        <v>13</v>
+      </c>
+      <c r="D362" t="s">
+        <v>18</v>
+      </c>
+      <c r="E362" t="s">
+        <v>19</v>
+      </c>
+      <c r="F362" t="s">
+        <v>46</v>
+      </c>
+      <c r="G362">
+        <v>10235</v>
+      </c>
+    </row>
     <row r="771" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G771" s="2"/>
     </row>

--- a/datos_reales.xlsx
+++ b/datos_reales.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acfestadistica\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32AB9EE9-7E8F-486A-9731-5CE0F559C8EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{801A0E68-ADD5-432F-9257-4D2BBD38A8EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1451" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1567" uniqueCount="51">
   <si>
     <t>AÑO</t>
   </si>
@@ -8903,6 +8903,673 @@
         <v>10235</v>
       </c>
     </row>
+    <row r="363" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A363">
+        <v>2026</v>
+      </c>
+      <c r="B363" t="s">
+        <v>49</v>
+      </c>
+      <c r="C363">
+        <v>14</v>
+      </c>
+      <c r="D363" t="s">
+        <v>8</v>
+      </c>
+      <c r="E363" t="s">
+        <v>19</v>
+      </c>
+      <c r="F363" t="s">
+        <v>20</v>
+      </c>
+      <c r="G363">
+        <v>7350</v>
+      </c>
+    </row>
+    <row r="364" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A364">
+        <v>2026</v>
+      </c>
+      <c r="B364" t="s">
+        <v>49</v>
+      </c>
+      <c r="C364">
+        <v>14</v>
+      </c>
+      <c r="D364" t="s">
+        <v>8</v>
+      </c>
+      <c r="E364" t="s">
+        <v>19</v>
+      </c>
+      <c r="F364" t="s">
+        <v>21</v>
+      </c>
+      <c r="G364">
+        <v>15433</v>
+      </c>
+    </row>
+    <row r="365" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A365">
+        <v>2026</v>
+      </c>
+      <c r="B365" t="s">
+        <v>49</v>
+      </c>
+      <c r="C365">
+        <v>14</v>
+      </c>
+      <c r="D365" t="s">
+        <v>8</v>
+      </c>
+      <c r="E365" t="s">
+        <v>19</v>
+      </c>
+      <c r="F365" t="s">
+        <v>22</v>
+      </c>
+      <c r="G365">
+        <v>5570</v>
+      </c>
+    </row>
+    <row r="366" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A366">
+        <v>2026</v>
+      </c>
+      <c r="B366" t="s">
+        <v>49</v>
+      </c>
+      <c r="C366">
+        <v>14</v>
+      </c>
+      <c r="D366" t="s">
+        <v>8</v>
+      </c>
+      <c r="E366" t="s">
+        <v>19</v>
+      </c>
+      <c r="F366" t="s">
+        <v>47</v>
+      </c>
+      <c r="G366">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="367" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A367">
+        <v>2026</v>
+      </c>
+      <c r="B367" t="s">
+        <v>49</v>
+      </c>
+      <c r="C367">
+        <v>14</v>
+      </c>
+      <c r="D367" t="s">
+        <v>9</v>
+      </c>
+      <c r="E367" t="s">
+        <v>19</v>
+      </c>
+      <c r="F367" t="s">
+        <v>23</v>
+      </c>
+      <c r="G367">
+        <v>3099</v>
+      </c>
+    </row>
+    <row r="368" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A368">
+        <v>2026</v>
+      </c>
+      <c r="B368" t="s">
+        <v>49</v>
+      </c>
+      <c r="C368">
+        <v>14</v>
+      </c>
+      <c r="D368" t="s">
+        <v>11</v>
+      </c>
+      <c r="E368" t="s">
+        <v>19</v>
+      </c>
+      <c r="F368" t="s">
+        <v>25</v>
+      </c>
+      <c r="G368">
+        <v>2760</v>
+      </c>
+    </row>
+    <row r="369" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A369">
+        <v>2026</v>
+      </c>
+      <c r="B369" t="s">
+        <v>49</v>
+      </c>
+      <c r="C369">
+        <v>14</v>
+      </c>
+      <c r="D369" t="s">
+        <v>11</v>
+      </c>
+      <c r="E369" t="s">
+        <v>19</v>
+      </c>
+      <c r="F369" t="s">
+        <v>24</v>
+      </c>
+      <c r="G369">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="370" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A370">
+        <v>2026</v>
+      </c>
+      <c r="B370" t="s">
+        <v>49</v>
+      </c>
+      <c r="C370">
+        <v>14</v>
+      </c>
+      <c r="D370" t="s">
+        <v>12</v>
+      </c>
+      <c r="E370" t="s">
+        <v>19</v>
+      </c>
+      <c r="F370" t="s">
+        <v>26</v>
+      </c>
+      <c r="G370">
+        <v>18190</v>
+      </c>
+    </row>
+    <row r="371" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A371">
+        <v>2026</v>
+      </c>
+      <c r="B371" t="s">
+        <v>49</v>
+      </c>
+      <c r="C371">
+        <v>14</v>
+      </c>
+      <c r="D371" t="s">
+        <v>12</v>
+      </c>
+      <c r="E371" t="s">
+        <v>19</v>
+      </c>
+      <c r="F371" t="s">
+        <v>27</v>
+      </c>
+      <c r="G371">
+        <v>5760</v>
+      </c>
+    </row>
+    <row r="372" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A372">
+        <v>2026</v>
+      </c>
+      <c r="B372" t="s">
+        <v>49</v>
+      </c>
+      <c r="C372">
+        <v>14</v>
+      </c>
+      <c r="D372" t="s">
+        <v>12</v>
+      </c>
+      <c r="E372" t="s">
+        <v>19</v>
+      </c>
+      <c r="F372" t="s">
+        <v>28</v>
+      </c>
+      <c r="G372">
+        <v>5037</v>
+      </c>
+    </row>
+    <row r="373" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A373">
+        <v>2026</v>
+      </c>
+      <c r="B373" t="s">
+        <v>49</v>
+      </c>
+      <c r="C373">
+        <v>14</v>
+      </c>
+      <c r="D373" t="s">
+        <v>12</v>
+      </c>
+      <c r="E373" t="s">
+        <v>19</v>
+      </c>
+      <c r="F373" t="s">
+        <v>29</v>
+      </c>
+      <c r="G373">
+        <v>7122</v>
+      </c>
+    </row>
+    <row r="374" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A374">
+        <v>2026</v>
+      </c>
+      <c r="B374" t="s">
+        <v>49</v>
+      </c>
+      <c r="C374">
+        <v>14</v>
+      </c>
+      <c r="D374" t="s">
+        <v>13</v>
+      </c>
+      <c r="E374" t="s">
+        <v>19</v>
+      </c>
+      <c r="F374" t="s">
+        <v>30</v>
+      </c>
+      <c r="G374">
+        <v>2665</v>
+      </c>
+    </row>
+    <row r="375" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A375">
+        <v>2026</v>
+      </c>
+      <c r="B375" t="s">
+        <v>49</v>
+      </c>
+      <c r="C375">
+        <v>14</v>
+      </c>
+      <c r="D375" t="s">
+        <v>14</v>
+      </c>
+      <c r="E375" t="s">
+        <v>19</v>
+      </c>
+      <c r="F375" t="s">
+        <v>31</v>
+      </c>
+      <c r="G375">
+        <v>3480</v>
+      </c>
+    </row>
+    <row r="376" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A376">
+        <v>2026</v>
+      </c>
+      <c r="B376" t="s">
+        <v>49</v>
+      </c>
+      <c r="C376">
+        <v>14</v>
+      </c>
+      <c r="D376" t="s">
+        <v>14</v>
+      </c>
+      <c r="E376" t="s">
+        <v>19</v>
+      </c>
+      <c r="F376" t="s">
+        <v>32</v>
+      </c>
+      <c r="G376">
+        <v>13270</v>
+      </c>
+    </row>
+    <row r="377" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A377">
+        <v>2026</v>
+      </c>
+      <c r="B377" t="s">
+        <v>49</v>
+      </c>
+      <c r="C377">
+        <v>14</v>
+      </c>
+      <c r="D377" t="s">
+        <v>14</v>
+      </c>
+      <c r="E377" t="s">
+        <v>19</v>
+      </c>
+      <c r="F377" t="s">
+        <v>33</v>
+      </c>
+      <c r="G377">
+        <v>11514</v>
+      </c>
+    </row>
+    <row r="378" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A378">
+        <v>2026</v>
+      </c>
+      <c r="B378" t="s">
+        <v>49</v>
+      </c>
+      <c r="C378">
+        <v>14</v>
+      </c>
+      <c r="D378" t="s">
+        <v>15</v>
+      </c>
+      <c r="E378" t="s">
+        <v>19</v>
+      </c>
+      <c r="F378" t="s">
+        <v>34</v>
+      </c>
+      <c r="G378">
+        <v>20340</v>
+      </c>
+    </row>
+    <row r="379" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A379">
+        <v>2026</v>
+      </c>
+      <c r="B379" t="s">
+        <v>49</v>
+      </c>
+      <c r="C379">
+        <v>14</v>
+      </c>
+      <c r="D379" t="s">
+        <v>15</v>
+      </c>
+      <c r="E379" t="s">
+        <v>19</v>
+      </c>
+      <c r="F379" t="s">
+        <v>35</v>
+      </c>
+      <c r="G379">
+        <v>10925</v>
+      </c>
+    </row>
+    <row r="380" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A380">
+        <v>2026</v>
+      </c>
+      <c r="B380" t="s">
+        <v>49</v>
+      </c>
+      <c r="C380">
+        <v>14</v>
+      </c>
+      <c r="D380" t="s">
+        <v>16</v>
+      </c>
+      <c r="E380" t="s">
+        <v>19</v>
+      </c>
+      <c r="F380" t="s">
+        <v>36</v>
+      </c>
+      <c r="G380">
+        <v>4390</v>
+      </c>
+    </row>
+    <row r="381" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A381">
+        <v>2026</v>
+      </c>
+      <c r="B381" t="s">
+        <v>49</v>
+      </c>
+      <c r="C381">
+        <v>14</v>
+      </c>
+      <c r="D381" t="s">
+        <v>16</v>
+      </c>
+      <c r="E381" t="s">
+        <v>19</v>
+      </c>
+      <c r="F381" t="s">
+        <v>37</v>
+      </c>
+      <c r="G381">
+        <v>4012</v>
+      </c>
+    </row>
+    <row r="382" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A382">
+        <v>2026</v>
+      </c>
+      <c r="B382" t="s">
+        <v>49</v>
+      </c>
+      <c r="C382">
+        <v>14</v>
+      </c>
+      <c r="D382" t="s">
+        <v>16</v>
+      </c>
+      <c r="E382" t="s">
+        <v>19</v>
+      </c>
+      <c r="F382" t="s">
+        <v>38</v>
+      </c>
+      <c r="G382">
+        <v>2160</v>
+      </c>
+    </row>
+    <row r="383" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A383">
+        <v>2026</v>
+      </c>
+      <c r="B383" t="s">
+        <v>49</v>
+      </c>
+      <c r="C383">
+        <v>14</v>
+      </c>
+      <c r="D383" t="s">
+        <v>16</v>
+      </c>
+      <c r="E383" t="s">
+        <v>19</v>
+      </c>
+      <c r="F383" t="s">
+        <v>39</v>
+      </c>
+      <c r="G383">
+        <v>21266</v>
+      </c>
+    </row>
+    <row r="384" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A384">
+        <v>2026</v>
+      </c>
+      <c r="B384" t="s">
+        <v>49</v>
+      </c>
+      <c r="C384">
+        <v>14</v>
+      </c>
+      <c r="D384" t="s">
+        <v>17</v>
+      </c>
+      <c r="E384" t="s">
+        <v>17</v>
+      </c>
+      <c r="F384" t="s">
+        <v>40</v>
+      </c>
+      <c r="G384">
+        <v>136422</v>
+      </c>
+    </row>
+    <row r="385" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A385">
+        <v>2026</v>
+      </c>
+      <c r="B385" t="s">
+        <v>49</v>
+      </c>
+      <c r="C385">
+        <v>14</v>
+      </c>
+      <c r="D385" t="s">
+        <v>17</v>
+      </c>
+      <c r="E385" t="s">
+        <v>17</v>
+      </c>
+      <c r="F385" t="s">
+        <v>50</v>
+      </c>
+      <c r="G385">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="386" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A386">
+        <v>2026</v>
+      </c>
+      <c r="B386" t="s">
+        <v>49</v>
+      </c>
+      <c r="C386">
+        <v>14</v>
+      </c>
+      <c r="D386" t="s">
+        <v>18</v>
+      </c>
+      <c r="E386" t="s">
+        <v>19</v>
+      </c>
+      <c r="F386" t="s">
+        <v>41</v>
+      </c>
+      <c r="G386">
+        <v>5920</v>
+      </c>
+    </row>
+    <row r="387" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A387">
+        <v>2026</v>
+      </c>
+      <c r="B387" t="s">
+        <v>49</v>
+      </c>
+      <c r="C387">
+        <v>14</v>
+      </c>
+      <c r="D387" t="s">
+        <v>18</v>
+      </c>
+      <c r="E387" t="s">
+        <v>19</v>
+      </c>
+      <c r="F387" t="s">
+        <v>42</v>
+      </c>
+      <c r="G387">
+        <v>12860</v>
+      </c>
+    </row>
+    <row r="388" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A388">
+        <v>2026</v>
+      </c>
+      <c r="B388" t="s">
+        <v>49</v>
+      </c>
+      <c r="C388">
+        <v>14</v>
+      </c>
+      <c r="D388" t="s">
+        <v>18</v>
+      </c>
+      <c r="E388" t="s">
+        <v>19</v>
+      </c>
+      <c r="F388" t="s">
+        <v>43</v>
+      </c>
+      <c r="G388">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="389" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A389">
+        <v>2026</v>
+      </c>
+      <c r="B389" t="s">
+        <v>49</v>
+      </c>
+      <c r="C389">
+        <v>14</v>
+      </c>
+      <c r="D389" t="s">
+        <v>18</v>
+      </c>
+      <c r="E389" t="s">
+        <v>19</v>
+      </c>
+      <c r="F389" t="s">
+        <v>44</v>
+      </c>
+      <c r="G389">
+        <v>3521</v>
+      </c>
+    </row>
+    <row r="390" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A390">
+        <v>2026</v>
+      </c>
+      <c r="B390" t="s">
+        <v>49</v>
+      </c>
+      <c r="C390">
+        <v>14</v>
+      </c>
+      <c r="D390" t="s">
+        <v>18</v>
+      </c>
+      <c r="E390" t="s">
+        <v>19</v>
+      </c>
+      <c r="F390" t="s">
+        <v>45</v>
+      </c>
+      <c r="G390">
+        <v>6797</v>
+      </c>
+    </row>
+    <row r="391" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A391">
+        <v>2026</v>
+      </c>
+      <c r="B391" t="s">
+        <v>49</v>
+      </c>
+      <c r="C391">
+        <v>14</v>
+      </c>
+      <c r="D391" t="s">
+        <v>18</v>
+      </c>
+      <c r="E391" t="s">
+        <v>19</v>
+      </c>
+      <c r="F391" t="s">
+        <v>46</v>
+      </c>
+      <c r="G391">
+        <v>12137</v>
+      </c>
+    </row>
     <row r="771" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G771" s="2"/>
     </row>

--- a/datos_reales.xlsx
+++ b/datos_reales.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acfestadistica\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{801A0E68-ADD5-432F-9257-4D2BBD38A8EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{599FB840-B809-433D-8FE1-DFCFF69AFB16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1567" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1683" uniqueCount="52">
   <si>
     <t>AÑO</t>
   </si>
@@ -189,6 +189,9 @@
   </si>
   <si>
     <t>REDVOLUTION</t>
+  </si>
+  <si>
+    <t>ABRIL</t>
   </si>
 </sst>
 </file>
@@ -8908,7 +8911,7 @@
         <v>2026</v>
       </c>
       <c r="B363" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C363">
         <v>14</v>
@@ -8931,7 +8934,7 @@
         <v>2026</v>
       </c>
       <c r="B364" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C364">
         <v>14</v>
@@ -8954,7 +8957,7 @@
         <v>2026</v>
       </c>
       <c r="B365" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C365">
         <v>14</v>
@@ -8977,7 +8980,7 @@
         <v>2026</v>
       </c>
       <c r="B366" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C366">
         <v>14</v>
@@ -9000,7 +9003,7 @@
         <v>2026</v>
       </c>
       <c r="B367" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C367">
         <v>14</v>
@@ -9023,7 +9026,7 @@
         <v>2026</v>
       </c>
       <c r="B368" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C368">
         <v>14</v>
@@ -9046,7 +9049,7 @@
         <v>2026</v>
       </c>
       <c r="B369" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C369">
         <v>14</v>
@@ -9069,7 +9072,7 @@
         <v>2026</v>
       </c>
       <c r="B370" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C370">
         <v>14</v>
@@ -9092,7 +9095,7 @@
         <v>2026</v>
       </c>
       <c r="B371" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C371">
         <v>14</v>
@@ -9115,7 +9118,7 @@
         <v>2026</v>
       </c>
       <c r="B372" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C372">
         <v>14</v>
@@ -9138,7 +9141,7 @@
         <v>2026</v>
       </c>
       <c r="B373" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C373">
         <v>14</v>
@@ -9161,7 +9164,7 @@
         <v>2026</v>
       </c>
       <c r="B374" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C374">
         <v>14</v>
@@ -9184,7 +9187,7 @@
         <v>2026</v>
       </c>
       <c r="B375" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C375">
         <v>14</v>
@@ -9207,7 +9210,7 @@
         <v>2026</v>
       </c>
       <c r="B376" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C376">
         <v>14</v>
@@ -9230,7 +9233,7 @@
         <v>2026</v>
       </c>
       <c r="B377" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C377">
         <v>14</v>
@@ -9253,7 +9256,7 @@
         <v>2026</v>
       </c>
       <c r="B378" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C378">
         <v>14</v>
@@ -9276,7 +9279,7 @@
         <v>2026</v>
       </c>
       <c r="B379" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C379">
         <v>14</v>
@@ -9299,7 +9302,7 @@
         <v>2026</v>
       </c>
       <c r="B380" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C380">
         <v>14</v>
@@ -9322,7 +9325,7 @@
         <v>2026</v>
       </c>
       <c r="B381" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C381">
         <v>14</v>
@@ -9345,7 +9348,7 @@
         <v>2026</v>
       </c>
       <c r="B382" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C382">
         <v>14</v>
@@ -9368,7 +9371,7 @@
         <v>2026</v>
       </c>
       <c r="B383" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C383">
         <v>14</v>
@@ -9391,7 +9394,7 @@
         <v>2026</v>
       </c>
       <c r="B384" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C384">
         <v>14</v>
@@ -9414,7 +9417,7 @@
         <v>2026</v>
       </c>
       <c r="B385" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C385">
         <v>14</v>
@@ -9437,7 +9440,7 @@
         <v>2026</v>
       </c>
       <c r="B386" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C386">
         <v>14</v>
@@ -9460,7 +9463,7 @@
         <v>2026</v>
       </c>
       <c r="B387" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C387">
         <v>14</v>
@@ -9483,7 +9486,7 @@
         <v>2026</v>
       </c>
       <c r="B388" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C388">
         <v>14</v>
@@ -9506,7 +9509,7 @@
         <v>2026</v>
       </c>
       <c r="B389" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C389">
         <v>14</v>
@@ -9529,7 +9532,7 @@
         <v>2026</v>
       </c>
       <c r="B390" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C390">
         <v>14</v>
@@ -9552,7 +9555,7 @@
         <v>2026</v>
       </c>
       <c r="B391" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C391">
         <v>14</v>
@@ -9568,6 +9571,673 @@
       </c>
       <c r="G391">
         <v>12137</v>
+      </c>
+    </row>
+    <row r="392" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A392">
+        <v>2026</v>
+      </c>
+      <c r="B392" t="s">
+        <v>51</v>
+      </c>
+      <c r="C392">
+        <v>15</v>
+      </c>
+      <c r="D392" t="s">
+        <v>8</v>
+      </c>
+      <c r="E392" t="s">
+        <v>19</v>
+      </c>
+      <c r="F392" t="s">
+        <v>20</v>
+      </c>
+      <c r="G392">
+        <v>8456</v>
+      </c>
+    </row>
+    <row r="393" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A393">
+        <v>2026</v>
+      </c>
+      <c r="B393" t="s">
+        <v>51</v>
+      </c>
+      <c r="C393">
+        <v>15</v>
+      </c>
+      <c r="D393" t="s">
+        <v>8</v>
+      </c>
+      <c r="E393" t="s">
+        <v>19</v>
+      </c>
+      <c r="F393" t="s">
+        <v>21</v>
+      </c>
+      <c r="G393">
+        <v>16570</v>
+      </c>
+    </row>
+    <row r="394" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A394">
+        <v>2026</v>
+      </c>
+      <c r="B394" t="s">
+        <v>51</v>
+      </c>
+      <c r="C394">
+        <v>15</v>
+      </c>
+      <c r="D394" t="s">
+        <v>8</v>
+      </c>
+      <c r="E394" t="s">
+        <v>19</v>
+      </c>
+      <c r="F394" t="s">
+        <v>22</v>
+      </c>
+      <c r="G394">
+        <v>5085</v>
+      </c>
+    </row>
+    <row r="395" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A395">
+        <v>2026</v>
+      </c>
+      <c r="B395" t="s">
+        <v>51</v>
+      </c>
+      <c r="C395">
+        <v>15</v>
+      </c>
+      <c r="D395" t="s">
+        <v>8</v>
+      </c>
+      <c r="E395" t="s">
+        <v>19</v>
+      </c>
+      <c r="F395" t="s">
+        <v>47</v>
+      </c>
+      <c r="G395">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="396" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A396">
+        <v>2026</v>
+      </c>
+      <c r="B396" t="s">
+        <v>51</v>
+      </c>
+      <c r="C396">
+        <v>15</v>
+      </c>
+      <c r="D396" t="s">
+        <v>9</v>
+      </c>
+      <c r="E396" t="s">
+        <v>19</v>
+      </c>
+      <c r="F396" t="s">
+        <v>23</v>
+      </c>
+      <c r="G396">
+        <v>3327</v>
+      </c>
+    </row>
+    <row r="397" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A397">
+        <v>2026</v>
+      </c>
+      <c r="B397" t="s">
+        <v>51</v>
+      </c>
+      <c r="C397">
+        <v>15</v>
+      </c>
+      <c r="D397" t="s">
+        <v>11</v>
+      </c>
+      <c r="E397" t="s">
+        <v>19</v>
+      </c>
+      <c r="F397" t="s">
+        <v>25</v>
+      </c>
+      <c r="G397">
+        <v>3254</v>
+      </c>
+    </row>
+    <row r="398" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A398">
+        <v>2026</v>
+      </c>
+      <c r="B398" t="s">
+        <v>51</v>
+      </c>
+      <c r="C398">
+        <v>15</v>
+      </c>
+      <c r="D398" t="s">
+        <v>11</v>
+      </c>
+      <c r="E398" t="s">
+        <v>19</v>
+      </c>
+      <c r="F398" t="s">
+        <v>24</v>
+      </c>
+      <c r="G398">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="399" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A399">
+        <v>2026</v>
+      </c>
+      <c r="B399" t="s">
+        <v>51</v>
+      </c>
+      <c r="C399">
+        <v>15</v>
+      </c>
+      <c r="D399" t="s">
+        <v>12</v>
+      </c>
+      <c r="E399" t="s">
+        <v>19</v>
+      </c>
+      <c r="F399" t="s">
+        <v>26</v>
+      </c>
+      <c r="G399">
+        <v>17150</v>
+      </c>
+    </row>
+    <row r="400" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A400">
+        <v>2026</v>
+      </c>
+      <c r="B400" t="s">
+        <v>51</v>
+      </c>
+      <c r="C400">
+        <v>15</v>
+      </c>
+      <c r="D400" t="s">
+        <v>12</v>
+      </c>
+      <c r="E400" t="s">
+        <v>19</v>
+      </c>
+      <c r="F400" t="s">
+        <v>27</v>
+      </c>
+      <c r="G400">
+        <v>7404</v>
+      </c>
+    </row>
+    <row r="401" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A401">
+        <v>2026</v>
+      </c>
+      <c r="B401" t="s">
+        <v>51</v>
+      </c>
+      <c r="C401">
+        <v>15</v>
+      </c>
+      <c r="D401" t="s">
+        <v>12</v>
+      </c>
+      <c r="E401" t="s">
+        <v>19</v>
+      </c>
+      <c r="F401" t="s">
+        <v>28</v>
+      </c>
+      <c r="G401">
+        <v>11440</v>
+      </c>
+    </row>
+    <row r="402" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A402">
+        <v>2026</v>
+      </c>
+      <c r="B402" t="s">
+        <v>51</v>
+      </c>
+      <c r="C402">
+        <v>15</v>
+      </c>
+      <c r="D402" t="s">
+        <v>12</v>
+      </c>
+      <c r="E402" t="s">
+        <v>19</v>
+      </c>
+      <c r="F402" t="s">
+        <v>29</v>
+      </c>
+      <c r="G402">
+        <v>7960</v>
+      </c>
+    </row>
+    <row r="403" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A403">
+        <v>2026</v>
+      </c>
+      <c r="B403" t="s">
+        <v>51</v>
+      </c>
+      <c r="C403">
+        <v>15</v>
+      </c>
+      <c r="D403" t="s">
+        <v>13</v>
+      </c>
+      <c r="E403" t="s">
+        <v>19</v>
+      </c>
+      <c r="F403" t="s">
+        <v>30</v>
+      </c>
+      <c r="G403">
+        <v>3883</v>
+      </c>
+    </row>
+    <row r="404" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A404">
+        <v>2026</v>
+      </c>
+      <c r="B404" t="s">
+        <v>51</v>
+      </c>
+      <c r="C404">
+        <v>15</v>
+      </c>
+      <c r="D404" t="s">
+        <v>14</v>
+      </c>
+      <c r="E404" t="s">
+        <v>19</v>
+      </c>
+      <c r="F404" t="s">
+        <v>31</v>
+      </c>
+      <c r="G404">
+        <v>4547</v>
+      </c>
+    </row>
+    <row r="405" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A405">
+        <v>2026</v>
+      </c>
+      <c r="B405" t="s">
+        <v>51</v>
+      </c>
+      <c r="C405">
+        <v>15</v>
+      </c>
+      <c r="D405" t="s">
+        <v>14</v>
+      </c>
+      <c r="E405" t="s">
+        <v>19</v>
+      </c>
+      <c r="F405" t="s">
+        <v>32</v>
+      </c>
+      <c r="G405">
+        <v>14808</v>
+      </c>
+    </row>
+    <row r="406" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A406">
+        <v>2026</v>
+      </c>
+      <c r="B406" t="s">
+        <v>51</v>
+      </c>
+      <c r="C406">
+        <v>15</v>
+      </c>
+      <c r="D406" t="s">
+        <v>14</v>
+      </c>
+      <c r="E406" t="s">
+        <v>19</v>
+      </c>
+      <c r="F406" t="s">
+        <v>33</v>
+      </c>
+      <c r="G406">
+        <v>12840</v>
+      </c>
+    </row>
+    <row r="407" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A407">
+        <v>2026</v>
+      </c>
+      <c r="B407" t="s">
+        <v>51</v>
+      </c>
+      <c r="C407">
+        <v>15</v>
+      </c>
+      <c r="D407" t="s">
+        <v>15</v>
+      </c>
+      <c r="E407" t="s">
+        <v>19</v>
+      </c>
+      <c r="F407" t="s">
+        <v>34</v>
+      </c>
+      <c r="G407">
+        <v>26750</v>
+      </c>
+    </row>
+    <row r="408" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A408">
+        <v>2026</v>
+      </c>
+      <c r="B408" t="s">
+        <v>51</v>
+      </c>
+      <c r="C408">
+        <v>15</v>
+      </c>
+      <c r="D408" t="s">
+        <v>15</v>
+      </c>
+      <c r="E408" t="s">
+        <v>19</v>
+      </c>
+      <c r="F408" t="s">
+        <v>35</v>
+      </c>
+      <c r="G408">
+        <v>11400</v>
+      </c>
+    </row>
+    <row r="409" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A409">
+        <v>2026</v>
+      </c>
+      <c r="B409" t="s">
+        <v>51</v>
+      </c>
+      <c r="C409">
+        <v>15</v>
+      </c>
+      <c r="D409" t="s">
+        <v>16</v>
+      </c>
+      <c r="E409" t="s">
+        <v>19</v>
+      </c>
+      <c r="F409" t="s">
+        <v>36</v>
+      </c>
+      <c r="G409">
+        <v>4170</v>
+      </c>
+    </row>
+    <row r="410" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A410">
+        <v>2026</v>
+      </c>
+      <c r="B410" t="s">
+        <v>51</v>
+      </c>
+      <c r="C410">
+        <v>15</v>
+      </c>
+      <c r="D410" t="s">
+        <v>16</v>
+      </c>
+      <c r="E410" t="s">
+        <v>19</v>
+      </c>
+      <c r="F410" t="s">
+        <v>37</v>
+      </c>
+      <c r="G410">
+        <v>5150</v>
+      </c>
+    </row>
+    <row r="411" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A411">
+        <v>2026</v>
+      </c>
+      <c r="B411" t="s">
+        <v>51</v>
+      </c>
+      <c r="C411">
+        <v>15</v>
+      </c>
+      <c r="D411" t="s">
+        <v>16</v>
+      </c>
+      <c r="E411" t="s">
+        <v>19</v>
+      </c>
+      <c r="F411" t="s">
+        <v>38</v>
+      </c>
+      <c r="G411">
+        <v>3050</v>
+      </c>
+    </row>
+    <row r="412" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A412">
+        <v>2026</v>
+      </c>
+      <c r="B412" t="s">
+        <v>51</v>
+      </c>
+      <c r="C412">
+        <v>15</v>
+      </c>
+      <c r="D412" t="s">
+        <v>16</v>
+      </c>
+      <c r="E412" t="s">
+        <v>19</v>
+      </c>
+      <c r="F412" t="s">
+        <v>39</v>
+      </c>
+      <c r="G412">
+        <v>22410</v>
+      </c>
+    </row>
+    <row r="413" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A413">
+        <v>2026</v>
+      </c>
+      <c r="B413" t="s">
+        <v>51</v>
+      </c>
+      <c r="C413">
+        <v>15</v>
+      </c>
+      <c r="D413" t="s">
+        <v>17</v>
+      </c>
+      <c r="E413" t="s">
+        <v>17</v>
+      </c>
+      <c r="F413" t="s">
+        <v>40</v>
+      </c>
+      <c r="G413">
+        <v>180114</v>
+      </c>
+    </row>
+    <row r="414" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A414">
+        <v>2026</v>
+      </c>
+      <c r="B414" t="s">
+        <v>51</v>
+      </c>
+      <c r="C414">
+        <v>15</v>
+      </c>
+      <c r="D414" t="s">
+        <v>17</v>
+      </c>
+      <c r="E414" t="s">
+        <v>17</v>
+      </c>
+      <c r="F414" t="s">
+        <v>50</v>
+      </c>
+      <c r="G414">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="415" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A415">
+        <v>2026</v>
+      </c>
+      <c r="B415" t="s">
+        <v>51</v>
+      </c>
+      <c r="C415">
+        <v>15</v>
+      </c>
+      <c r="D415" t="s">
+        <v>18</v>
+      </c>
+      <c r="E415" t="s">
+        <v>19</v>
+      </c>
+      <c r="F415" t="s">
+        <v>41</v>
+      </c>
+      <c r="G415">
+        <v>7320</v>
+      </c>
+    </row>
+    <row r="416" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A416">
+        <v>2026</v>
+      </c>
+      <c r="B416" t="s">
+        <v>51</v>
+      </c>
+      <c r="C416">
+        <v>15</v>
+      </c>
+      <c r="D416" t="s">
+        <v>18</v>
+      </c>
+      <c r="E416" t="s">
+        <v>19</v>
+      </c>
+      <c r="F416" t="s">
+        <v>42</v>
+      </c>
+      <c r="G416">
+        <v>17540</v>
+      </c>
+    </row>
+    <row r="417" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A417">
+        <v>2026</v>
+      </c>
+      <c r="B417" t="s">
+        <v>51</v>
+      </c>
+      <c r="C417">
+        <v>15</v>
+      </c>
+      <c r="D417" t="s">
+        <v>18</v>
+      </c>
+      <c r="E417" t="s">
+        <v>19</v>
+      </c>
+      <c r="F417" t="s">
+        <v>43</v>
+      </c>
+      <c r="G417">
+        <v>2760</v>
+      </c>
+    </row>
+    <row r="418" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A418">
+        <v>2026</v>
+      </c>
+      <c r="B418" t="s">
+        <v>51</v>
+      </c>
+      <c r="C418">
+        <v>15</v>
+      </c>
+      <c r="D418" t="s">
+        <v>18</v>
+      </c>
+      <c r="E418" t="s">
+        <v>19</v>
+      </c>
+      <c r="F418" t="s">
+        <v>44</v>
+      </c>
+      <c r="G418">
+        <v>4780</v>
+      </c>
+    </row>
+    <row r="419" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A419">
+        <v>2026</v>
+      </c>
+      <c r="B419" t="s">
+        <v>51</v>
+      </c>
+      <c r="C419">
+        <v>15</v>
+      </c>
+      <c r="D419" t="s">
+        <v>18</v>
+      </c>
+      <c r="E419" t="s">
+        <v>19</v>
+      </c>
+      <c r="F419" t="s">
+        <v>45</v>
+      </c>
+      <c r="G419">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="420" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A420">
+        <v>2026</v>
+      </c>
+      <c r="B420" t="s">
+        <v>51</v>
+      </c>
+      <c r="C420">
+        <v>15</v>
+      </c>
+      <c r="D420" t="s">
+        <v>18</v>
+      </c>
+      <c r="E420" t="s">
+        <v>19</v>
+      </c>
+      <c r="F420" t="s">
+        <v>46</v>
+      </c>
+      <c r="G420">
+        <v>17027</v>
       </c>
     </row>
     <row r="771" spans="7:7" x14ac:dyDescent="0.25">

--- a/datos_reales.xlsx
+++ b/datos_reales.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acfestadistica\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{599FB840-B809-433D-8FE1-DFCFF69AFB16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81FB2457-1B5E-4DA4-B922-53A4766C028E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1683" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1803" uniqueCount="53">
   <si>
     <t>AÑO</t>
   </si>
@@ -192,6 +192,9 @@
   </si>
   <si>
     <t>ABRIL</t>
+  </si>
+  <si>
+    <t>SUMMER ROMANCE</t>
   </si>
 </sst>
 </file>
@@ -10240,6 +10243,696 @@
         <v>17027</v>
       </c>
     </row>
+    <row r="421" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A421">
+        <v>2026</v>
+      </c>
+      <c r="B421" t="s">
+        <v>51</v>
+      </c>
+      <c r="C421">
+        <v>16</v>
+      </c>
+      <c r="D421" t="s">
+        <v>8</v>
+      </c>
+      <c r="E421" t="s">
+        <v>19</v>
+      </c>
+      <c r="F421" t="s">
+        <v>20</v>
+      </c>
+      <c r="G421">
+        <v>13282</v>
+      </c>
+    </row>
+    <row r="422" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A422">
+        <v>2026</v>
+      </c>
+      <c r="B422" t="s">
+        <v>51</v>
+      </c>
+      <c r="C422">
+        <v>16</v>
+      </c>
+      <c r="D422" t="s">
+        <v>8</v>
+      </c>
+      <c r="E422" t="s">
+        <v>19</v>
+      </c>
+      <c r="F422" t="s">
+        <v>21</v>
+      </c>
+      <c r="G422">
+        <v>26651</v>
+      </c>
+    </row>
+    <row r="423" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A423">
+        <v>2026</v>
+      </c>
+      <c r="B423" t="s">
+        <v>51</v>
+      </c>
+      <c r="C423">
+        <v>16</v>
+      </c>
+      <c r="D423" t="s">
+        <v>8</v>
+      </c>
+      <c r="E423" t="s">
+        <v>19</v>
+      </c>
+      <c r="F423" t="s">
+        <v>22</v>
+      </c>
+      <c r="G423">
+        <v>10401</v>
+      </c>
+    </row>
+    <row r="424" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A424">
+        <v>2026</v>
+      </c>
+      <c r="B424" t="s">
+        <v>51</v>
+      </c>
+      <c r="C424">
+        <v>16</v>
+      </c>
+      <c r="D424" t="s">
+        <v>8</v>
+      </c>
+      <c r="E424" t="s">
+        <v>19</v>
+      </c>
+      <c r="F424" t="s">
+        <v>52</v>
+      </c>
+      <c r="G424">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="425" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A425">
+        <v>2026</v>
+      </c>
+      <c r="B425" t="s">
+        <v>51</v>
+      </c>
+      <c r="C425">
+        <v>16</v>
+      </c>
+      <c r="D425" t="s">
+        <v>8</v>
+      </c>
+      <c r="E425" t="s">
+        <v>19</v>
+      </c>
+      <c r="F425" t="s">
+        <v>47</v>
+      </c>
+      <c r="G425">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="426" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A426">
+        <v>2026</v>
+      </c>
+      <c r="B426" t="s">
+        <v>51</v>
+      </c>
+      <c r="C426">
+        <v>16</v>
+      </c>
+      <c r="D426" t="s">
+        <v>9</v>
+      </c>
+      <c r="E426" t="s">
+        <v>19</v>
+      </c>
+      <c r="F426" t="s">
+        <v>23</v>
+      </c>
+      <c r="G426">
+        <v>7050</v>
+      </c>
+    </row>
+    <row r="427" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A427">
+        <v>2026</v>
+      </c>
+      <c r="B427" t="s">
+        <v>51</v>
+      </c>
+      <c r="C427">
+        <v>16</v>
+      </c>
+      <c r="D427" t="s">
+        <v>11</v>
+      </c>
+      <c r="E427" t="s">
+        <v>19</v>
+      </c>
+      <c r="F427" t="s">
+        <v>25</v>
+      </c>
+      <c r="G427">
+        <v>3930</v>
+      </c>
+    </row>
+    <row r="428" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A428">
+        <v>2026</v>
+      </c>
+      <c r="B428" t="s">
+        <v>51</v>
+      </c>
+      <c r="C428">
+        <v>16</v>
+      </c>
+      <c r="D428" t="s">
+        <v>11</v>
+      </c>
+      <c r="E428" t="s">
+        <v>19</v>
+      </c>
+      <c r="F428" t="s">
+        <v>24</v>
+      </c>
+      <c r="G428">
+        <v>1775</v>
+      </c>
+    </row>
+    <row r="429" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A429">
+        <v>2026</v>
+      </c>
+      <c r="B429" t="s">
+        <v>51</v>
+      </c>
+      <c r="C429">
+        <v>16</v>
+      </c>
+      <c r="D429" t="s">
+        <v>12</v>
+      </c>
+      <c r="E429" t="s">
+        <v>19</v>
+      </c>
+      <c r="F429" t="s">
+        <v>26</v>
+      </c>
+      <c r="G429">
+        <v>26050</v>
+      </c>
+    </row>
+    <row r="430" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A430">
+        <v>2026</v>
+      </c>
+      <c r="B430" t="s">
+        <v>51</v>
+      </c>
+      <c r="C430">
+        <v>16</v>
+      </c>
+      <c r="D430" t="s">
+        <v>12</v>
+      </c>
+      <c r="E430" t="s">
+        <v>19</v>
+      </c>
+      <c r="F430" t="s">
+        <v>27</v>
+      </c>
+      <c r="G430">
+        <v>10173</v>
+      </c>
+    </row>
+    <row r="431" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A431">
+        <v>2026</v>
+      </c>
+      <c r="B431" t="s">
+        <v>51</v>
+      </c>
+      <c r="C431">
+        <v>16</v>
+      </c>
+      <c r="D431" t="s">
+        <v>12</v>
+      </c>
+      <c r="E431" t="s">
+        <v>19</v>
+      </c>
+      <c r="F431" t="s">
+        <v>28</v>
+      </c>
+      <c r="G431">
+        <v>17660</v>
+      </c>
+    </row>
+    <row r="432" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A432">
+        <v>2026</v>
+      </c>
+      <c r="B432" t="s">
+        <v>51</v>
+      </c>
+      <c r="C432">
+        <v>16</v>
+      </c>
+      <c r="D432" t="s">
+        <v>12</v>
+      </c>
+      <c r="E432" t="s">
+        <v>19</v>
+      </c>
+      <c r="F432" t="s">
+        <v>29</v>
+      </c>
+      <c r="G432">
+        <v>11492</v>
+      </c>
+    </row>
+    <row r="433" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A433">
+        <v>2026</v>
+      </c>
+      <c r="B433" t="s">
+        <v>51</v>
+      </c>
+      <c r="C433">
+        <v>16</v>
+      </c>
+      <c r="D433" t="s">
+        <v>13</v>
+      </c>
+      <c r="E433" t="s">
+        <v>19</v>
+      </c>
+      <c r="F433" t="s">
+        <v>30</v>
+      </c>
+      <c r="G433">
+        <v>5280</v>
+      </c>
+    </row>
+    <row r="434" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A434">
+        <v>2026</v>
+      </c>
+      <c r="B434" t="s">
+        <v>51</v>
+      </c>
+      <c r="C434">
+        <v>16</v>
+      </c>
+      <c r="D434" t="s">
+        <v>14</v>
+      </c>
+      <c r="E434" t="s">
+        <v>19</v>
+      </c>
+      <c r="F434" t="s">
+        <v>31</v>
+      </c>
+      <c r="G434">
+        <v>7150</v>
+      </c>
+    </row>
+    <row r="435" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A435">
+        <v>2026</v>
+      </c>
+      <c r="B435" t="s">
+        <v>51</v>
+      </c>
+      <c r="C435">
+        <v>16</v>
+      </c>
+      <c r="D435" t="s">
+        <v>14</v>
+      </c>
+      <c r="E435" t="s">
+        <v>19</v>
+      </c>
+      <c r="F435" t="s">
+        <v>32</v>
+      </c>
+      <c r="G435">
+        <v>20166</v>
+      </c>
+    </row>
+    <row r="436" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A436">
+        <v>2026</v>
+      </c>
+      <c r="B436" t="s">
+        <v>51</v>
+      </c>
+      <c r="C436">
+        <v>16</v>
+      </c>
+      <c r="D436" t="s">
+        <v>14</v>
+      </c>
+      <c r="E436" t="s">
+        <v>19</v>
+      </c>
+      <c r="F436" t="s">
+        <v>33</v>
+      </c>
+      <c r="G436">
+        <v>19785</v>
+      </c>
+    </row>
+    <row r="437" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A437">
+        <v>2026</v>
+      </c>
+      <c r="B437" t="s">
+        <v>51</v>
+      </c>
+      <c r="C437">
+        <v>16</v>
+      </c>
+      <c r="D437" t="s">
+        <v>15</v>
+      </c>
+      <c r="E437" t="s">
+        <v>19</v>
+      </c>
+      <c r="F437" t="s">
+        <v>34</v>
+      </c>
+      <c r="G437">
+        <v>34150</v>
+      </c>
+    </row>
+    <row r="438" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A438">
+        <v>2026</v>
+      </c>
+      <c r="B438" t="s">
+        <v>51</v>
+      </c>
+      <c r="C438">
+        <v>16</v>
+      </c>
+      <c r="D438" t="s">
+        <v>15</v>
+      </c>
+      <c r="E438" t="s">
+        <v>19</v>
+      </c>
+      <c r="F438" t="s">
+        <v>35</v>
+      </c>
+      <c r="G438">
+        <v>16550</v>
+      </c>
+    </row>
+    <row r="439" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A439">
+        <v>2026</v>
+      </c>
+      <c r="B439" t="s">
+        <v>51</v>
+      </c>
+      <c r="C439">
+        <v>16</v>
+      </c>
+      <c r="D439" t="s">
+        <v>16</v>
+      </c>
+      <c r="E439" t="s">
+        <v>19</v>
+      </c>
+      <c r="F439" t="s">
+        <v>36</v>
+      </c>
+      <c r="G439">
+        <v>7893</v>
+      </c>
+    </row>
+    <row r="440" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A440">
+        <v>2026</v>
+      </c>
+      <c r="B440" t="s">
+        <v>51</v>
+      </c>
+      <c r="C440">
+        <v>16</v>
+      </c>
+      <c r="D440" t="s">
+        <v>16</v>
+      </c>
+      <c r="E440" t="s">
+        <v>19</v>
+      </c>
+      <c r="F440" t="s">
+        <v>37</v>
+      </c>
+      <c r="G440">
+        <v>6174</v>
+      </c>
+    </row>
+    <row r="441" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A441">
+        <v>2026</v>
+      </c>
+      <c r="B441" t="s">
+        <v>51</v>
+      </c>
+      <c r="C441">
+        <v>16</v>
+      </c>
+      <c r="D441" t="s">
+        <v>16</v>
+      </c>
+      <c r="E441" t="s">
+        <v>19</v>
+      </c>
+      <c r="F441" t="s">
+        <v>38</v>
+      </c>
+      <c r="G441">
+        <v>6320</v>
+      </c>
+    </row>
+    <row r="442" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A442">
+        <v>2026</v>
+      </c>
+      <c r="B442" t="s">
+        <v>51</v>
+      </c>
+      <c r="C442">
+        <v>16</v>
+      </c>
+      <c r="D442" t="s">
+        <v>16</v>
+      </c>
+      <c r="E442" t="s">
+        <v>19</v>
+      </c>
+      <c r="F442" t="s">
+        <v>39</v>
+      </c>
+      <c r="G442">
+        <v>30037</v>
+      </c>
+    </row>
+    <row r="443" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A443">
+        <v>2026</v>
+      </c>
+      <c r="B443" t="s">
+        <v>51</v>
+      </c>
+      <c r="C443">
+        <v>16</v>
+      </c>
+      <c r="D443" t="s">
+        <v>17</v>
+      </c>
+      <c r="E443" t="s">
+        <v>17</v>
+      </c>
+      <c r="F443" t="s">
+        <v>40</v>
+      </c>
+      <c r="G443">
+        <v>222353</v>
+      </c>
+    </row>
+    <row r="444" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A444">
+        <v>2026</v>
+      </c>
+      <c r="B444" t="s">
+        <v>51</v>
+      </c>
+      <c r="C444">
+        <v>16</v>
+      </c>
+      <c r="D444" t="s">
+        <v>17</v>
+      </c>
+      <c r="E444" t="s">
+        <v>17</v>
+      </c>
+      <c r="F444" t="s">
+        <v>50</v>
+      </c>
+      <c r="G444">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="445" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A445">
+        <v>2026</v>
+      </c>
+      <c r="B445" t="s">
+        <v>51</v>
+      </c>
+      <c r="C445">
+        <v>16</v>
+      </c>
+      <c r="D445" t="s">
+        <v>18</v>
+      </c>
+      <c r="E445" t="s">
+        <v>19</v>
+      </c>
+      <c r="F445" t="s">
+        <v>41</v>
+      </c>
+      <c r="G445">
+        <v>9040</v>
+      </c>
+    </row>
+    <row r="446" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A446">
+        <v>2026</v>
+      </c>
+      <c r="B446" t="s">
+        <v>51</v>
+      </c>
+      <c r="C446">
+        <v>16</v>
+      </c>
+      <c r="D446" t="s">
+        <v>18</v>
+      </c>
+      <c r="E446" t="s">
+        <v>19</v>
+      </c>
+      <c r="F446" t="s">
+        <v>42</v>
+      </c>
+      <c r="G446">
+        <v>24300</v>
+      </c>
+    </row>
+    <row r="447" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A447">
+        <v>2026</v>
+      </c>
+      <c r="B447" t="s">
+        <v>51</v>
+      </c>
+      <c r="C447">
+        <v>16</v>
+      </c>
+      <c r="D447" t="s">
+        <v>18</v>
+      </c>
+      <c r="E447" t="s">
+        <v>19</v>
+      </c>
+      <c r="F447" t="s">
+        <v>43</v>
+      </c>
+      <c r="G447">
+        <v>2865</v>
+      </c>
+    </row>
+    <row r="448" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A448">
+        <v>2026</v>
+      </c>
+      <c r="B448" t="s">
+        <v>51</v>
+      </c>
+      <c r="C448">
+        <v>16</v>
+      </c>
+      <c r="D448" t="s">
+        <v>18</v>
+      </c>
+      <c r="E448" t="s">
+        <v>19</v>
+      </c>
+      <c r="F448" t="s">
+        <v>44</v>
+      </c>
+      <c r="G448">
+        <v>6900</v>
+      </c>
+    </row>
+    <row r="449" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A449">
+        <v>2026</v>
+      </c>
+      <c r="B449" t="s">
+        <v>51</v>
+      </c>
+      <c r="C449">
+        <v>16</v>
+      </c>
+      <c r="D449" t="s">
+        <v>18</v>
+      </c>
+      <c r="E449" t="s">
+        <v>19</v>
+      </c>
+      <c r="F449" t="s">
+        <v>45</v>
+      </c>
+      <c r="G449">
+        <v>10120</v>
+      </c>
+    </row>
+    <row r="450" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A450">
+        <v>2026</v>
+      </c>
+      <c r="B450" t="s">
+        <v>51</v>
+      </c>
+      <c r="C450">
+        <v>16</v>
+      </c>
+      <c r="D450" t="s">
+        <v>18</v>
+      </c>
+      <c r="E450" t="s">
+        <v>19</v>
+      </c>
+      <c r="F450" t="s">
+        <v>46</v>
+      </c>
+      <c r="G450">
+        <v>19294</v>
+      </c>
+    </row>
     <row r="771" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G771" s="2"/>
     </row>

--- a/datos_reales.xlsx
+++ b/datos_reales.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acfestadistica\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81FB2457-1B5E-4DA4-B922-53A4766C028E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADEA32FA-806A-4393-9C29-E61095515CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1803" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1919" uniqueCount="53">
   <si>
     <t>AÑO</t>
   </si>
@@ -10933,6 +10933,673 @@
         <v>19294</v>
       </c>
     </row>
+    <row r="451" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A451">
+        <v>2026</v>
+      </c>
+      <c r="B451" t="s">
+        <v>51</v>
+      </c>
+      <c r="C451">
+        <v>17</v>
+      </c>
+      <c r="D451" t="s">
+        <v>8</v>
+      </c>
+      <c r="E451" t="s">
+        <v>19</v>
+      </c>
+      <c r="F451" t="s">
+        <v>20</v>
+      </c>
+      <c r="G451">
+        <v>9196</v>
+      </c>
+    </row>
+    <row r="452" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A452">
+        <v>2026</v>
+      </c>
+      <c r="B452" t="s">
+        <v>51</v>
+      </c>
+      <c r="C452">
+        <v>17</v>
+      </c>
+      <c r="D452" t="s">
+        <v>8</v>
+      </c>
+      <c r="E452" t="s">
+        <v>19</v>
+      </c>
+      <c r="F452" t="s">
+        <v>21</v>
+      </c>
+      <c r="G452">
+        <v>20594</v>
+      </c>
+    </row>
+    <row r="453" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A453">
+        <v>2026</v>
+      </c>
+      <c r="B453" t="s">
+        <v>51</v>
+      </c>
+      <c r="C453">
+        <v>17</v>
+      </c>
+      <c r="D453" t="s">
+        <v>8</v>
+      </c>
+      <c r="E453" t="s">
+        <v>19</v>
+      </c>
+      <c r="F453" t="s">
+        <v>22</v>
+      </c>
+      <c r="G453">
+        <v>14687</v>
+      </c>
+    </row>
+    <row r="454" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A454">
+        <v>2026</v>
+      </c>
+      <c r="B454" t="s">
+        <v>51</v>
+      </c>
+      <c r="C454">
+        <v>17</v>
+      </c>
+      <c r="D454" t="s">
+        <v>8</v>
+      </c>
+      <c r="E454" t="s">
+        <v>19</v>
+      </c>
+      <c r="F454" t="s">
+        <v>47</v>
+      </c>
+      <c r="G454">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="455" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A455">
+        <v>2026</v>
+      </c>
+      <c r="B455" t="s">
+        <v>51</v>
+      </c>
+      <c r="C455">
+        <v>17</v>
+      </c>
+      <c r="D455" t="s">
+        <v>9</v>
+      </c>
+      <c r="E455" t="s">
+        <v>19</v>
+      </c>
+      <c r="F455" t="s">
+        <v>23</v>
+      </c>
+      <c r="G455">
+        <v>10508</v>
+      </c>
+    </row>
+    <row r="456" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A456">
+        <v>2026</v>
+      </c>
+      <c r="B456" t="s">
+        <v>51</v>
+      </c>
+      <c r="C456">
+        <v>17</v>
+      </c>
+      <c r="D456" t="s">
+        <v>11</v>
+      </c>
+      <c r="E456" t="s">
+        <v>19</v>
+      </c>
+      <c r="F456" t="s">
+        <v>25</v>
+      </c>
+      <c r="G456">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="457" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A457">
+        <v>2026</v>
+      </c>
+      <c r="B457" t="s">
+        <v>51</v>
+      </c>
+      <c r="C457">
+        <v>17</v>
+      </c>
+      <c r="D457" t="s">
+        <v>11</v>
+      </c>
+      <c r="E457" t="s">
+        <v>19</v>
+      </c>
+      <c r="F457" t="s">
+        <v>24</v>
+      </c>
+      <c r="G457">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="458" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A458">
+        <v>2026</v>
+      </c>
+      <c r="B458" t="s">
+        <v>51</v>
+      </c>
+      <c r="C458">
+        <v>17</v>
+      </c>
+      <c r="D458" t="s">
+        <v>12</v>
+      </c>
+      <c r="E458" t="s">
+        <v>19</v>
+      </c>
+      <c r="F458" t="s">
+        <v>26</v>
+      </c>
+      <c r="G458">
+        <v>19223</v>
+      </c>
+    </row>
+    <row r="459" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A459">
+        <v>2026</v>
+      </c>
+      <c r="B459" t="s">
+        <v>51</v>
+      </c>
+      <c r="C459">
+        <v>17</v>
+      </c>
+      <c r="D459" t="s">
+        <v>12</v>
+      </c>
+      <c r="E459" t="s">
+        <v>19</v>
+      </c>
+      <c r="F459" t="s">
+        <v>27</v>
+      </c>
+      <c r="G459">
+        <v>7591</v>
+      </c>
+    </row>
+    <row r="460" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A460">
+        <v>2026</v>
+      </c>
+      <c r="B460" t="s">
+        <v>51</v>
+      </c>
+      <c r="C460">
+        <v>17</v>
+      </c>
+      <c r="D460" t="s">
+        <v>12</v>
+      </c>
+      <c r="E460" t="s">
+        <v>19</v>
+      </c>
+      <c r="F460" t="s">
+        <v>28</v>
+      </c>
+      <c r="G460">
+        <v>12200</v>
+      </c>
+    </row>
+    <row r="461" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A461">
+        <v>2026</v>
+      </c>
+      <c r="B461" t="s">
+        <v>51</v>
+      </c>
+      <c r="C461">
+        <v>17</v>
+      </c>
+      <c r="D461" t="s">
+        <v>12</v>
+      </c>
+      <c r="E461" t="s">
+        <v>19</v>
+      </c>
+      <c r="F461" t="s">
+        <v>29</v>
+      </c>
+      <c r="G461">
+        <v>9982</v>
+      </c>
+    </row>
+    <row r="462" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A462">
+        <v>2026</v>
+      </c>
+      <c r="B462" t="s">
+        <v>51</v>
+      </c>
+      <c r="C462">
+        <v>17</v>
+      </c>
+      <c r="D462" t="s">
+        <v>13</v>
+      </c>
+      <c r="E462" t="s">
+        <v>19</v>
+      </c>
+      <c r="F462" t="s">
+        <v>30</v>
+      </c>
+      <c r="G462">
+        <v>4323</v>
+      </c>
+    </row>
+    <row r="463" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A463">
+        <v>2026</v>
+      </c>
+      <c r="B463" t="s">
+        <v>51</v>
+      </c>
+      <c r="C463">
+        <v>17</v>
+      </c>
+      <c r="D463" t="s">
+        <v>14</v>
+      </c>
+      <c r="E463" t="s">
+        <v>19</v>
+      </c>
+      <c r="F463" t="s">
+        <v>31</v>
+      </c>
+      <c r="G463">
+        <v>6840</v>
+      </c>
+    </row>
+    <row r="464" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A464">
+        <v>2026</v>
+      </c>
+      <c r="B464" t="s">
+        <v>51</v>
+      </c>
+      <c r="C464">
+        <v>17</v>
+      </c>
+      <c r="D464" t="s">
+        <v>14</v>
+      </c>
+      <c r="E464" t="s">
+        <v>19</v>
+      </c>
+      <c r="F464" t="s">
+        <v>32</v>
+      </c>
+      <c r="G464">
+        <v>24235</v>
+      </c>
+    </row>
+    <row r="465" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A465">
+        <v>2026</v>
+      </c>
+      <c r="B465" t="s">
+        <v>51</v>
+      </c>
+      <c r="C465">
+        <v>17</v>
+      </c>
+      <c r="D465" t="s">
+        <v>14</v>
+      </c>
+      <c r="E465" t="s">
+        <v>19</v>
+      </c>
+      <c r="F465" t="s">
+        <v>33</v>
+      </c>
+      <c r="G465">
+        <v>23180</v>
+      </c>
+    </row>
+    <row r="466" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A466">
+        <v>2026</v>
+      </c>
+      <c r="B466" t="s">
+        <v>51</v>
+      </c>
+      <c r="C466">
+        <v>17</v>
+      </c>
+      <c r="D466" t="s">
+        <v>15</v>
+      </c>
+      <c r="E466" t="s">
+        <v>19</v>
+      </c>
+      <c r="F466" t="s">
+        <v>34</v>
+      </c>
+      <c r="G466">
+        <v>26800</v>
+      </c>
+    </row>
+    <row r="467" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A467">
+        <v>2026</v>
+      </c>
+      <c r="B467" t="s">
+        <v>51</v>
+      </c>
+      <c r="C467">
+        <v>17</v>
+      </c>
+      <c r="D467" t="s">
+        <v>15</v>
+      </c>
+      <c r="E467" t="s">
+        <v>19</v>
+      </c>
+      <c r="F467" t="s">
+        <v>35</v>
+      </c>
+      <c r="G467">
+        <v>12172</v>
+      </c>
+    </row>
+    <row r="468" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A468">
+        <v>2026</v>
+      </c>
+      <c r="B468" t="s">
+        <v>51</v>
+      </c>
+      <c r="C468">
+        <v>17</v>
+      </c>
+      <c r="D468" t="s">
+        <v>16</v>
+      </c>
+      <c r="E468" t="s">
+        <v>19</v>
+      </c>
+      <c r="F468" t="s">
+        <v>36</v>
+      </c>
+      <c r="G468">
+        <v>5942</v>
+      </c>
+    </row>
+    <row r="469" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A469">
+        <v>2026</v>
+      </c>
+      <c r="B469" t="s">
+        <v>51</v>
+      </c>
+      <c r="C469">
+        <v>17</v>
+      </c>
+      <c r="D469" t="s">
+        <v>16</v>
+      </c>
+      <c r="E469" t="s">
+        <v>19</v>
+      </c>
+      <c r="F469" t="s">
+        <v>37</v>
+      </c>
+      <c r="G469">
+        <v>4860</v>
+      </c>
+    </row>
+    <row r="470" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A470">
+        <v>2026</v>
+      </c>
+      <c r="B470" t="s">
+        <v>51</v>
+      </c>
+      <c r="C470">
+        <v>17</v>
+      </c>
+      <c r="D470" t="s">
+        <v>16</v>
+      </c>
+      <c r="E470" t="s">
+        <v>19</v>
+      </c>
+      <c r="F470" t="s">
+        <v>38</v>
+      </c>
+      <c r="G470">
+        <v>6640</v>
+      </c>
+    </row>
+    <row r="471" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A471">
+        <v>2026</v>
+      </c>
+      <c r="B471" t="s">
+        <v>51</v>
+      </c>
+      <c r="C471">
+        <v>17</v>
+      </c>
+      <c r="D471" t="s">
+        <v>16</v>
+      </c>
+      <c r="E471" t="s">
+        <v>19</v>
+      </c>
+      <c r="F471" t="s">
+        <v>39</v>
+      </c>
+      <c r="G471">
+        <v>33247</v>
+      </c>
+    </row>
+    <row r="472" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A472">
+        <v>2026</v>
+      </c>
+      <c r="B472" t="s">
+        <v>51</v>
+      </c>
+      <c r="C472">
+        <v>17</v>
+      </c>
+      <c r="D472" t="s">
+        <v>17</v>
+      </c>
+      <c r="E472" t="s">
+        <v>17</v>
+      </c>
+      <c r="F472" t="s">
+        <v>40</v>
+      </c>
+      <c r="G472">
+        <v>221204</v>
+      </c>
+    </row>
+    <row r="473" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A473">
+        <v>2026</v>
+      </c>
+      <c r="B473" t="s">
+        <v>51</v>
+      </c>
+      <c r="C473">
+        <v>17</v>
+      </c>
+      <c r="D473" t="s">
+        <v>17</v>
+      </c>
+      <c r="E473" t="s">
+        <v>17</v>
+      </c>
+      <c r="F473" t="s">
+        <v>50</v>
+      </c>
+      <c r="G473">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="474" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A474">
+        <v>2026</v>
+      </c>
+      <c r="B474" t="s">
+        <v>51</v>
+      </c>
+      <c r="C474">
+        <v>17</v>
+      </c>
+      <c r="D474" t="s">
+        <v>18</v>
+      </c>
+      <c r="E474" t="s">
+        <v>19</v>
+      </c>
+      <c r="F474" t="s">
+        <v>41</v>
+      </c>
+      <c r="G474">
+        <v>8500</v>
+      </c>
+    </row>
+    <row r="475" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A475">
+        <v>2026</v>
+      </c>
+      <c r="B475" t="s">
+        <v>51</v>
+      </c>
+      <c r="C475">
+        <v>17</v>
+      </c>
+      <c r="D475" t="s">
+        <v>18</v>
+      </c>
+      <c r="E475" t="s">
+        <v>19</v>
+      </c>
+      <c r="F475" t="s">
+        <v>42</v>
+      </c>
+      <c r="G475">
+        <v>18245</v>
+      </c>
+    </row>
+    <row r="476" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A476">
+        <v>2026</v>
+      </c>
+      <c r="B476" t="s">
+        <v>51</v>
+      </c>
+      <c r="C476">
+        <v>17</v>
+      </c>
+      <c r="D476" t="s">
+        <v>18</v>
+      </c>
+      <c r="E476" t="s">
+        <v>19</v>
+      </c>
+      <c r="F476" t="s">
+        <v>43</v>
+      </c>
+      <c r="G476">
+        <v>2640</v>
+      </c>
+    </row>
+    <row r="477" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A477">
+        <v>2026</v>
+      </c>
+      <c r="B477" t="s">
+        <v>51</v>
+      </c>
+      <c r="C477">
+        <v>17</v>
+      </c>
+      <c r="D477" t="s">
+        <v>18</v>
+      </c>
+      <c r="E477" t="s">
+        <v>19</v>
+      </c>
+      <c r="F477" t="s">
+        <v>44</v>
+      </c>
+      <c r="G477">
+        <v>5130</v>
+      </c>
+    </row>
+    <row r="478" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A478">
+        <v>2026</v>
+      </c>
+      <c r="B478" t="s">
+        <v>51</v>
+      </c>
+      <c r="C478">
+        <v>17</v>
+      </c>
+      <c r="D478" t="s">
+        <v>18</v>
+      </c>
+      <c r="E478" t="s">
+        <v>19</v>
+      </c>
+      <c r="F478" t="s">
+        <v>45</v>
+      </c>
+      <c r="G478">
+        <v>9412</v>
+      </c>
+    </row>
+    <row r="479" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A479">
+        <v>2026</v>
+      </c>
+      <c r="B479" t="s">
+        <v>51</v>
+      </c>
+      <c r="C479">
+        <v>17</v>
+      </c>
+      <c r="D479" t="s">
+        <v>18</v>
+      </c>
+      <c r="E479" t="s">
+        <v>19</v>
+      </c>
+      <c r="F479" t="s">
+        <v>46</v>
+      </c>
+      <c r="G479">
+        <v>14685</v>
+      </c>
+    </row>
     <row r="771" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G771" s="2"/>
     </row>

--- a/datos_reales.xlsx
+++ b/datos_reales.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acfestadistica\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADEA32FA-806A-4393-9C29-E61095515CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0735B1E-ECBC-465E-9EFC-2C0851089C14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1919" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2035" uniqueCount="53">
   <si>
     <t>AÑO</t>
   </si>
@@ -11600,6 +11600,673 @@
         <v>14685</v>
       </c>
     </row>
+    <row r="480" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A480">
+        <v>2026</v>
+      </c>
+      <c r="B480" t="s">
+        <v>51</v>
+      </c>
+      <c r="C480">
+        <v>18</v>
+      </c>
+      <c r="D480" t="s">
+        <v>8</v>
+      </c>
+      <c r="E480" t="s">
+        <v>19</v>
+      </c>
+      <c r="F480" t="s">
+        <v>20</v>
+      </c>
+      <c r="G480">
+        <v>7510</v>
+      </c>
+    </row>
+    <row r="481" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A481">
+        <v>2026</v>
+      </c>
+      <c r="B481" t="s">
+        <v>51</v>
+      </c>
+      <c r="C481">
+        <v>18</v>
+      </c>
+      <c r="D481" t="s">
+        <v>8</v>
+      </c>
+      <c r="E481" t="s">
+        <v>19</v>
+      </c>
+      <c r="F481" t="s">
+        <v>21</v>
+      </c>
+      <c r="G481">
+        <v>16185</v>
+      </c>
+    </row>
+    <row r="482" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A482">
+        <v>2026</v>
+      </c>
+      <c r="B482" t="s">
+        <v>51</v>
+      </c>
+      <c r="C482">
+        <v>18</v>
+      </c>
+      <c r="D482" t="s">
+        <v>8</v>
+      </c>
+      <c r="E482" t="s">
+        <v>19</v>
+      </c>
+      <c r="F482" t="s">
+        <v>22</v>
+      </c>
+      <c r="G482">
+        <v>7670</v>
+      </c>
+    </row>
+    <row r="483" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A483">
+        <v>2026</v>
+      </c>
+      <c r="B483" t="s">
+        <v>51</v>
+      </c>
+      <c r="C483">
+        <v>18</v>
+      </c>
+      <c r="D483" t="s">
+        <v>8</v>
+      </c>
+      <c r="E483" t="s">
+        <v>19</v>
+      </c>
+      <c r="F483" t="s">
+        <v>47</v>
+      </c>
+      <c r="G483">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="484" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A484">
+        <v>2026</v>
+      </c>
+      <c r="B484" t="s">
+        <v>51</v>
+      </c>
+      <c r="C484">
+        <v>18</v>
+      </c>
+      <c r="D484" t="s">
+        <v>9</v>
+      </c>
+      <c r="E484" t="s">
+        <v>19</v>
+      </c>
+      <c r="F484" t="s">
+        <v>23</v>
+      </c>
+      <c r="G484">
+        <v>6950</v>
+      </c>
+    </row>
+    <row r="485" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A485">
+        <v>2026</v>
+      </c>
+      <c r="B485" t="s">
+        <v>51</v>
+      </c>
+      <c r="C485">
+        <v>18</v>
+      </c>
+      <c r="D485" t="s">
+        <v>11</v>
+      </c>
+      <c r="E485" t="s">
+        <v>19</v>
+      </c>
+      <c r="F485" t="s">
+        <v>25</v>
+      </c>
+      <c r="G485">
+        <v>2230</v>
+      </c>
+    </row>
+    <row r="486" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A486">
+        <v>2026</v>
+      </c>
+      <c r="B486" t="s">
+        <v>51</v>
+      </c>
+      <c r="C486">
+        <v>18</v>
+      </c>
+      <c r="D486" t="s">
+        <v>11</v>
+      </c>
+      <c r="E486" t="s">
+        <v>19</v>
+      </c>
+      <c r="F486" t="s">
+        <v>24</v>
+      </c>
+      <c r="G486">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="487" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A487">
+        <v>2026</v>
+      </c>
+      <c r="B487" t="s">
+        <v>51</v>
+      </c>
+      <c r="C487">
+        <v>18</v>
+      </c>
+      <c r="D487" t="s">
+        <v>12</v>
+      </c>
+      <c r="E487" t="s">
+        <v>19</v>
+      </c>
+      <c r="F487" t="s">
+        <v>26</v>
+      </c>
+      <c r="G487">
+        <v>16822</v>
+      </c>
+    </row>
+    <row r="488" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A488">
+        <v>2026</v>
+      </c>
+      <c r="B488" t="s">
+        <v>51</v>
+      </c>
+      <c r="C488">
+        <v>18</v>
+      </c>
+      <c r="D488" t="s">
+        <v>12</v>
+      </c>
+      <c r="E488" t="s">
+        <v>19</v>
+      </c>
+      <c r="F488" t="s">
+        <v>27</v>
+      </c>
+      <c r="G488">
+        <v>4900</v>
+      </c>
+    </row>
+    <row r="489" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A489">
+        <v>2026</v>
+      </c>
+      <c r="B489" t="s">
+        <v>51</v>
+      </c>
+      <c r="C489">
+        <v>18</v>
+      </c>
+      <c r="D489" t="s">
+        <v>12</v>
+      </c>
+      <c r="E489" t="s">
+        <v>19</v>
+      </c>
+      <c r="F489" t="s">
+        <v>28</v>
+      </c>
+      <c r="G489">
+        <v>10650</v>
+      </c>
+    </row>
+    <row r="490" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A490">
+        <v>2026</v>
+      </c>
+      <c r="B490" t="s">
+        <v>51</v>
+      </c>
+      <c r="C490">
+        <v>18</v>
+      </c>
+      <c r="D490" t="s">
+        <v>12</v>
+      </c>
+      <c r="E490" t="s">
+        <v>19</v>
+      </c>
+      <c r="F490" t="s">
+        <v>29</v>
+      </c>
+      <c r="G490">
+        <v>6409</v>
+      </c>
+    </row>
+    <row r="491" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A491">
+        <v>2026</v>
+      </c>
+      <c r="B491" t="s">
+        <v>51</v>
+      </c>
+      <c r="C491">
+        <v>18</v>
+      </c>
+      <c r="D491" t="s">
+        <v>13</v>
+      </c>
+      <c r="E491" t="s">
+        <v>19</v>
+      </c>
+      <c r="F491" t="s">
+        <v>30</v>
+      </c>
+      <c r="G491">
+        <v>3100</v>
+      </c>
+    </row>
+    <row r="492" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A492">
+        <v>2026</v>
+      </c>
+      <c r="B492" t="s">
+        <v>51</v>
+      </c>
+      <c r="C492">
+        <v>18</v>
+      </c>
+      <c r="D492" t="s">
+        <v>14</v>
+      </c>
+      <c r="E492" t="s">
+        <v>19</v>
+      </c>
+      <c r="F492" t="s">
+        <v>31</v>
+      </c>
+      <c r="G492">
+        <v>5166</v>
+      </c>
+    </row>
+    <row r="493" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A493">
+        <v>2026</v>
+      </c>
+      <c r="B493" t="s">
+        <v>51</v>
+      </c>
+      <c r="C493">
+        <v>18</v>
+      </c>
+      <c r="D493" t="s">
+        <v>14</v>
+      </c>
+      <c r="E493" t="s">
+        <v>19</v>
+      </c>
+      <c r="F493" t="s">
+        <v>32</v>
+      </c>
+      <c r="G493">
+        <v>14438</v>
+      </c>
+    </row>
+    <row r="494" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A494">
+        <v>2026</v>
+      </c>
+      <c r="B494" t="s">
+        <v>51</v>
+      </c>
+      <c r="C494">
+        <v>18</v>
+      </c>
+      <c r="D494" t="s">
+        <v>14</v>
+      </c>
+      <c r="E494" t="s">
+        <v>19</v>
+      </c>
+      <c r="F494" t="s">
+        <v>33</v>
+      </c>
+      <c r="G494">
+        <v>16024</v>
+      </c>
+    </row>
+    <row r="495" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A495">
+        <v>2026</v>
+      </c>
+      <c r="B495" t="s">
+        <v>51</v>
+      </c>
+      <c r="C495">
+        <v>18</v>
+      </c>
+      <c r="D495" t="s">
+        <v>15</v>
+      </c>
+      <c r="E495" t="s">
+        <v>19</v>
+      </c>
+      <c r="F495" t="s">
+        <v>34</v>
+      </c>
+      <c r="G495">
+        <v>19210</v>
+      </c>
+    </row>
+    <row r="496" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A496">
+        <v>2026</v>
+      </c>
+      <c r="B496" t="s">
+        <v>51</v>
+      </c>
+      <c r="C496">
+        <v>18</v>
+      </c>
+      <c r="D496" t="s">
+        <v>15</v>
+      </c>
+      <c r="E496" t="s">
+        <v>19</v>
+      </c>
+      <c r="F496" t="s">
+        <v>35</v>
+      </c>
+      <c r="G496">
+        <v>9036</v>
+      </c>
+    </row>
+    <row r="497" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A497">
+        <v>2026</v>
+      </c>
+      <c r="B497" t="s">
+        <v>51</v>
+      </c>
+      <c r="C497">
+        <v>18</v>
+      </c>
+      <c r="D497" t="s">
+        <v>16</v>
+      </c>
+      <c r="E497" t="s">
+        <v>19</v>
+      </c>
+      <c r="F497" t="s">
+        <v>36</v>
+      </c>
+      <c r="G497">
+        <v>3111</v>
+      </c>
+    </row>
+    <row r="498" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A498">
+        <v>2026</v>
+      </c>
+      <c r="B498" t="s">
+        <v>51</v>
+      </c>
+      <c r="C498">
+        <v>18</v>
+      </c>
+      <c r="D498" t="s">
+        <v>16</v>
+      </c>
+      <c r="E498" t="s">
+        <v>19</v>
+      </c>
+      <c r="F498" t="s">
+        <v>37</v>
+      </c>
+      <c r="G498">
+        <v>3246</v>
+      </c>
+    </row>
+    <row r="499" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A499">
+        <v>2026</v>
+      </c>
+      <c r="B499" t="s">
+        <v>51</v>
+      </c>
+      <c r="C499">
+        <v>18</v>
+      </c>
+      <c r="D499" t="s">
+        <v>16</v>
+      </c>
+      <c r="E499" t="s">
+        <v>19</v>
+      </c>
+      <c r="F499" t="s">
+        <v>38</v>
+      </c>
+      <c r="G499">
+        <v>3890</v>
+      </c>
+    </row>
+    <row r="500" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A500">
+        <v>2026</v>
+      </c>
+      <c r="B500" t="s">
+        <v>51</v>
+      </c>
+      <c r="C500">
+        <v>18</v>
+      </c>
+      <c r="D500" t="s">
+        <v>16</v>
+      </c>
+      <c r="E500" t="s">
+        <v>19</v>
+      </c>
+      <c r="F500" t="s">
+        <v>39</v>
+      </c>
+      <c r="G500">
+        <v>26190</v>
+      </c>
+    </row>
+    <row r="501" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A501">
+        <v>2026</v>
+      </c>
+      <c r="B501" t="s">
+        <v>51</v>
+      </c>
+      <c r="C501">
+        <v>18</v>
+      </c>
+      <c r="D501" t="s">
+        <v>17</v>
+      </c>
+      <c r="E501" t="s">
+        <v>17</v>
+      </c>
+      <c r="F501" t="s">
+        <v>40</v>
+      </c>
+      <c r="G501">
+        <v>176813</v>
+      </c>
+    </row>
+    <row r="502" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A502">
+        <v>2026</v>
+      </c>
+      <c r="B502" t="s">
+        <v>51</v>
+      </c>
+      <c r="C502">
+        <v>18</v>
+      </c>
+      <c r="D502" t="s">
+        <v>17</v>
+      </c>
+      <c r="E502" t="s">
+        <v>17</v>
+      </c>
+      <c r="F502" t="s">
+        <v>50</v>
+      </c>
+      <c r="G502">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="503" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A503">
+        <v>2026</v>
+      </c>
+      <c r="B503" t="s">
+        <v>51</v>
+      </c>
+      <c r="C503">
+        <v>18</v>
+      </c>
+      <c r="D503" t="s">
+        <v>18</v>
+      </c>
+      <c r="E503" t="s">
+        <v>19</v>
+      </c>
+      <c r="F503" t="s">
+        <v>41</v>
+      </c>
+      <c r="G503">
+        <v>5893</v>
+      </c>
+    </row>
+    <row r="504" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A504">
+        <v>2026</v>
+      </c>
+      <c r="B504" t="s">
+        <v>51</v>
+      </c>
+      <c r="C504">
+        <v>18</v>
+      </c>
+      <c r="D504" t="s">
+        <v>18</v>
+      </c>
+      <c r="E504" t="s">
+        <v>19</v>
+      </c>
+      <c r="F504" t="s">
+        <v>42</v>
+      </c>
+      <c r="G504">
+        <v>14985</v>
+      </c>
+    </row>
+    <row r="505" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A505">
+        <v>2026</v>
+      </c>
+      <c r="B505" t="s">
+        <v>51</v>
+      </c>
+      <c r="C505">
+        <v>18</v>
+      </c>
+      <c r="D505" t="s">
+        <v>18</v>
+      </c>
+      <c r="E505" t="s">
+        <v>19</v>
+      </c>
+      <c r="F505" t="s">
+        <v>43</v>
+      </c>
+      <c r="G505">
+        <v>1852</v>
+      </c>
+    </row>
+    <row r="506" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A506">
+        <v>2026</v>
+      </c>
+      <c r="B506" t="s">
+        <v>51</v>
+      </c>
+      <c r="C506">
+        <v>18</v>
+      </c>
+      <c r="D506" t="s">
+        <v>18</v>
+      </c>
+      <c r="E506" t="s">
+        <v>19</v>
+      </c>
+      <c r="F506" t="s">
+        <v>44</v>
+      </c>
+      <c r="G506">
+        <v>3340</v>
+      </c>
+    </row>
+    <row r="507" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A507">
+        <v>2026</v>
+      </c>
+      <c r="B507" t="s">
+        <v>51</v>
+      </c>
+      <c r="C507">
+        <v>18</v>
+      </c>
+      <c r="D507" t="s">
+        <v>18</v>
+      </c>
+      <c r="E507" t="s">
+        <v>19</v>
+      </c>
+      <c r="F507" t="s">
+        <v>45</v>
+      </c>
+      <c r="G507">
+        <v>7230</v>
+      </c>
+    </row>
+    <row r="508" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A508">
+        <v>2026</v>
+      </c>
+      <c r="B508" t="s">
+        <v>51</v>
+      </c>
+      <c r="C508">
+        <v>18</v>
+      </c>
+      <c r="D508" t="s">
+        <v>18</v>
+      </c>
+      <c r="E508" t="s">
+        <v>19</v>
+      </c>
+      <c r="F508" t="s">
+        <v>46</v>
+      </c>
+      <c r="G508">
+        <v>9721</v>
+      </c>
+    </row>
     <row r="771" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G771" s="2"/>
     </row>
